--- a/2026/ANATOLE FRANCE/Abril/ANATOLE-Abril.xlsx
+++ b/2026/ANATOLE FRANCE/Abril/ANATOLE-Abril.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0320E407-505D-435F-BC05-6A9D383FBBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E642800-EF5C-4B3D-A83A-CB08EBC2F1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$128</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="184">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -199,9 +204,6 @@
     <t>CONSORCIO DE PROPIETARIOS ANATOLE FRANCE 1692</t>
   </si>
   <si>
-    <t>Seguro integral Allianz</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ascensores lema - Mantenimiento </t>
   </si>
   <si>
@@ -298,9 +300,6 @@
     <t>Pranteda Marta</t>
   </si>
   <si>
-    <t>Gil Delia (Cristina)</t>
-  </si>
-  <si>
     <t>Lopardo A</t>
   </si>
   <si>
@@ -358,12 +357,6 @@
     <t>Debito</t>
   </si>
   <si>
-    <t>Seguro integral Allianz - Accidentes personales Sr. Suplente</t>
-  </si>
-  <si>
-    <t>Adm Anterior</t>
-  </si>
-  <si>
     <t>Edesur</t>
   </si>
   <si>
@@ -391,9 +384,6 @@
     <t>Redondeo</t>
   </si>
   <si>
-    <t>Transf 26/02</t>
-  </si>
-  <si>
     <t>Alquiler Porteria</t>
   </si>
   <si>
@@ -466,21 +456,6 @@
     <t>Gustavo Padron - Sr contador</t>
   </si>
   <si>
-    <t>Transf 16/03</t>
-  </si>
-  <si>
-    <t>Transf 09/03</t>
-  </si>
-  <si>
-    <t>Transf 12/03</t>
-  </si>
-  <si>
-    <t>Transf 26/03</t>
-  </si>
-  <si>
-    <t>ARBA inmobiliaria - Partida nro. 0251265801</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fumigacion </t>
   </si>
   <si>
@@ -502,15 +477,6 @@
     <t>Leonardo y Dario</t>
   </si>
   <si>
-    <t>El mes anterior se le imputo un pago al 7C que era para el 1B</t>
-  </si>
-  <si>
-    <t>Deposito ya identificado mes anterior</t>
-  </si>
-  <si>
-    <t>Transferencia no identificada 09/03 Gabriel R. Mouriño</t>
-  </si>
-  <si>
     <t>Dpto:</t>
   </si>
   <si>
@@ -553,22 +519,70 @@
     <t>Transf 06/04</t>
   </si>
   <si>
-    <t>Honorarios Inmobiliaria</t>
-  </si>
-  <si>
     <t>Transf 13/04</t>
   </si>
   <si>
-    <t>Destapacion roman - Cloaca desde boca de acceso hacia caño troncal de AySa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Revisar algo relacionado con el pago - Pago $116.717,02 el 10 de marzo y nose si no se lo imputamos o que</t>
   </si>
   <si>
-    <t>Destapacion roman - Cloaca desde boca de acceso hacia caño troncal de AySa - Servicio de urgencia</t>
-  </si>
-  <si>
     <t>Transf 07/04</t>
+  </si>
+  <si>
+    <t>Federacion Patronal - Seguro de consorcio</t>
+  </si>
+  <si>
+    <t>Destapacion roman</t>
+  </si>
+  <si>
+    <t>Allianz Seguro - Mes anterior</t>
+  </si>
+  <si>
+    <t>AySa - Boca inspeccion calle</t>
+  </si>
+  <si>
+    <t>Transf 16 y 20/04</t>
+  </si>
+  <si>
+    <t>AySa - Destapacion</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>PROVEEDORES</t>
+  </si>
+  <si>
+    <t>Goldemberg Roxana - Sra. Abogada - Contestacion Carta documento 4A</t>
+  </si>
+  <si>
+    <t>Envio carta documento</t>
+  </si>
+  <si>
+    <t>Destapacion roman - Cloaca desde boca de acceso hacia caño troncal de AySa - Se extrajeron abundante cantidad de preservativos</t>
+  </si>
+  <si>
+    <t>Personal Flow</t>
+  </si>
+  <si>
+    <t>Honorarios inmobiliaria</t>
+  </si>
+  <si>
+    <t>Walter Martinez</t>
+  </si>
+  <si>
+    <t>Gabriel R Mouriño</t>
+  </si>
+  <si>
+    <t>Transferencia ya identificada mes anterior</t>
+  </si>
+  <si>
+    <t>Fracchia garcia Sebastian ezequiel</t>
+  </si>
+  <si>
+    <t>Pago ya identificado 1B</t>
+  </si>
+  <si>
+    <t>Se adeuda Marzo y Abril</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1284,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1423,9 +1437,6 @@
     </xf>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1508,7 +1519,6 @@
     <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="25" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1538,144 +1548,144 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1754,9 +1764,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1794,9 +1804,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1829,9 +1839,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1864,9 +1891,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2040,31 +2084,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M128"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M132"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="197" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
+      <c r="B1" s="203" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
       <c r="E1" s="61"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="62" t="s">
         <v>26</v>
@@ -2073,16 +2117,16 @@
       <c r="D2" s="62"/>
       <c r="E2" s="63"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="198" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="199"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="204" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="205"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -2093,12 +2137,12 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="62" t="s">
@@ -2106,7 +2150,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>56</v>
       </c>
@@ -2117,57 +2161,57 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="194" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" s="194"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="194"/>
-      <c r="C9" s="194"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="194"/>
-      <c r="C10" s="194"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="200" t="s">
-        <v>144</v>
-      </c>
-      <c r="B13" s="200"/>
-      <c r="C13" s="200"/>
-      <c r="D13" s="200"/>
-      <c r="E13" s="200"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="200"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="200"/>
-      <c r="D14" s="200"/>
-      <c r="E14" s="200"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="200"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="200"/>
-      <c r="D15" s="200"/>
-      <c r="E15" s="200"/>
-    </row>
-    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="200"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="200"/>
-      <c r="D16" s="200"/>
-      <c r="E16" s="200"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="200" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="200"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="206" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="206"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="206"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="206"/>
+      <c r="B15" s="206"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
+    </row>
+    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="206"/>
+      <c r="B16" s="206"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2176,7 +2220,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>31</v>
       </c>
@@ -2185,986 +2229,1029 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="195" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22" s="196"/>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="201" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="202"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="164">
-        <v>1012046.6</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D22" s="162">
+        <v>1038704</v>
+      </c>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23" s="115"/>
+        <v>115</v>
+      </c>
+      <c r="B23" s="114"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="164">
-        <v>-250481.55</v>
+      <c r="D23" s="162">
+        <v>-257079.24</v>
       </c>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="70" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="115"/>
+        <v>116</v>
+      </c>
+      <c r="B24" s="114"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="164">
-        <v>0.95</v>
+      <c r="D24" s="162">
+        <v>0.24</v>
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="54" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="54"/>
       <c r="C25" s="54"/>
-      <c r="D25" s="165">
+      <c r="D25" s="163">
         <f>SUM(D22:D24)</f>
-        <v>761566</v>
+        <v>781625</v>
       </c>
       <c r="E25" s="102"/>
       <c r="G25" s="21"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="164"/>
+      <c r="D26" s="162"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="164"/>
+      <c r="D27" s="162"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="164"/>
+      <c r="D28" s="162"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="166"/>
+      <c r="D29" s="164"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="166"/>
+      <c r="D30" s="164"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="54" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="54"/>
       <c r="C31" s="54"/>
-      <c r="D31" s="167">
+      <c r="D31" s="165">
         <f>SUM(D26:D30)</f>
         <v>0</v>
       </c>
       <c r="E31" s="102"/>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="29" t="s">
         <v>1</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
-      <c r="D32" s="168"/>
+      <c r="D32" s="166"/>
       <c r="E32" s="103">
         <f>D25+D31</f>
-        <v>761566</v>
+        <v>781625</v>
       </c>
       <c r="F32" s="21"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
-      <c r="D33" s="169"/>
+      <c r="D33" s="167"/>
       <c r="E33" s="104"/>
     </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="201" t="s">
-        <v>145</v>
-      </c>
-      <c r="B34" s="202"/>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="207" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="208"/>
       <c r="C34" s="51"/>
-      <c r="D34" s="242">
+      <c r="D34" s="162">
         <v>45000</v>
       </c>
       <c r="E34" s="105" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="201" t="s">
-        <v>114</v>
-      </c>
-      <c r="B35" s="202"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="208"/>
       <c r="C35" s="51"/>
-      <c r="D35" s="170">
-        <v>190000</v>
-      </c>
-      <c r="E35" s="105" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D35" s="168" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" s="105"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
         <v>15</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
-      <c r="D36" s="171"/>
+      <c r="D36" s="169"/>
       <c r="E36" s="106">
         <f>SUM(D34:D35)</f>
-        <v>235000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
         <v>29</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
-      <c r="D37" s="172"/>
+      <c r="D37" s="170"/>
       <c r="E37" s="107"/>
     </row>
-    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="195" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="196"/>
+    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="201" t="s">
+        <v>165</v>
+      </c>
+      <c r="B38" s="202"/>
       <c r="C38" s="52"/>
-      <c r="D38" s="173"/>
-      <c r="E38" s="122" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="195" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" s="196"/>
+      <c r="D38" s="171">
+        <v>161303</v>
+      </c>
+      <c r="E38" s="121" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="201" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" s="202"/>
       <c r="C39" s="52"/>
-      <c r="D39" s="174"/>
-      <c r="E39" s="108" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D39" s="172">
+        <v>200057</v>
+      </c>
+      <c r="E39" s="121" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
-      <c r="D40" s="171"/>
-      <c r="E40" s="109">
+      <c r="D40" s="169"/>
+      <c r="E40" s="108">
         <f>SUM(D38:D39)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>361360</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="110"/>
-      <c r="C41" s="110"/>
-      <c r="D41" s="175"/>
-      <c r="E41" s="111"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="109"/>
+      <c r="C41" s="109"/>
+      <c r="D41" s="173"/>
+      <c r="E41" s="110"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="51"/>
-      <c r="D42" s="241">
+      <c r="D42" s="199">
         <v>608782.14</v>
       </c>
-      <c r="E42" s="116" t="s">
-        <v>147</v>
+      <c r="E42" s="115" t="s">
+        <v>161</v>
       </c>
       <c r="G42" s="89"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="233">
+      <c r="D43" s="174">
         <v>45542.1</v>
       </c>
-      <c r="E43" s="116" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E43" s="115" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de ABRIL</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="233">
+      <c r="D44" s="174">
         <v>86489.03</v>
       </c>
-      <c r="E44" s="117" t="str">
+      <c r="E44" s="116" t="str">
         <f>E43</f>
-        <v>Transf 12/03</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>Transf 13/04</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de ABRIL</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="233">
+      <c r="D45" s="174">
         <v>5060.2299999999996</v>
       </c>
-      <c r="E45" s="118" t="str">
+      <c r="E45" s="117" t="str">
         <f>E43</f>
-        <v>Transf 12/03</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Transf 13/04</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="110"/>
-      <c r="C46" s="110"/>
-      <c r="D46" s="177"/>
-      <c r="E46" s="109">
+      <c r="B46" s="109"/>
+      <c r="C46" s="109"/>
+      <c r="D46" s="175"/>
+      <c r="E46" s="108">
         <f>SUM(D42:D45)</f>
         <v>745873.5</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="110"/>
-      <c r="C47" s="110"/>
-      <c r="D47" s="175"/>
-      <c r="E47" s="111"/>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="109"/>
+      <c r="C47" s="109"/>
+      <c r="D47" s="173"/>
+      <c r="E47" s="110"/>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="233">
+      <c r="D48" s="174">
         <v>299191.63</v>
       </c>
-      <c r="E48" s="116" t="s">
+      <c r="E48" s="115" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="196" t="s">
+        <v>176</v>
+      </c>
+      <c r="B49" s="197"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="174">
+        <v>49495.06</v>
+      </c>
+      <c r="E49" s="115" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="189" t="s">
+        <v>168</v>
+      </c>
+      <c r="B50" s="190"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="174">
+        <v>300000</v>
+      </c>
+      <c r="E50" s="115" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="189" t="s">
+        <v>170</v>
+      </c>
+      <c r="B51" s="190"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="174">
+        <v>80000</v>
+      </c>
+      <c r="E51" s="115" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="189" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52" s="190"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="174">
+        <v>999748.85</v>
+      </c>
+      <c r="E52" s="115" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="176"/>
+      <c r="E53" s="108">
+        <f>SUM(D48:D52)</f>
+        <v>1728435.54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="169"/>
+      <c r="E54" s="111"/>
+    </row>
+    <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="118" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="114"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="174">
+        <v>189500</v>
+      </c>
+      <c r="E55" s="146" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="118" t="s">
+        <v>158</v>
+      </c>
+      <c r="B56" s="114"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="174">
+        <v>31400</v>
+      </c>
+      <c r="E56" s="146" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="118" t="s">
+        <v>157</v>
+      </c>
+      <c r="B57" s="114"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="174">
+        <v>46200</v>
+      </c>
+      <c r="E57" s="146" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="118" t="s">
+        <v>159</v>
+      </c>
+      <c r="B58" s="114"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="174">
+        <v>31400</v>
+      </c>
+      <c r="E58" s="146" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="118" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" s="190"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="174">
+        <v>99500</v>
+      </c>
+      <c r="E59" s="146" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="118" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="195" t="s">
-        <v>113</v>
-      </c>
-      <c r="B49" s="196"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="233">
-        <v>999748.85</v>
-      </c>
-      <c r="E49" s="116" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="178"/>
-      <c r="E50" s="109">
-        <f>SUM(D48:D49)</f>
-        <v>1298940.48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="34"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="171"/>
-      <c r="E51" s="112"/>
-    </row>
-    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="119" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="115"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="176">
-        <v>175500</v>
-      </c>
-      <c r="E52" s="147" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="B53" s="115"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="176">
-        <v>10812.5</v>
-      </c>
-      <c r="E53" s="147" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="119" t="s">
-        <v>171</v>
-      </c>
-      <c r="B54" s="115"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="233">
-        <v>31400</v>
-      </c>
-      <c r="E54" s="147" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="119" t="s">
-        <v>170</v>
-      </c>
-      <c r="B55" s="115"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="233">
-        <v>31400</v>
-      </c>
-      <c r="E55" s="147" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="119" t="s">
-        <v>172</v>
-      </c>
-      <c r="B56" s="115"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="233">
-        <v>31400</v>
-      </c>
-      <c r="E56" s="147" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="119" t="s">
-        <v>151</v>
-      </c>
-      <c r="B57" s="115"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="233">
+      <c r="B60" s="190"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="174">
+        <v>22500</v>
+      </c>
+      <c r="E60" s="146" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="118" t="s">
+        <v>141</v>
+      </c>
+      <c r="B61" s="114"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="174">
         <v>60000</v>
       </c>
-      <c r="E57" s="147" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="195" t="s">
+      <c r="E61" s="146" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="191" t="s">
+        <v>166</v>
+      </c>
+      <c r="B62" s="114"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="174">
+        <v>85000</v>
+      </c>
+      <c r="E62" s="146" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="201" t="s">
         <v>175</v>
       </c>
-      <c r="B58" s="196"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="233">
-        <v>76800</v>
-      </c>
-      <c r="E58" s="147" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="240"/>
-      <c r="B59" s="115"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="233">
-        <v>80000</v>
-      </c>
-      <c r="E59" s="147" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="195" t="s">
-        <v>179</v>
-      </c>
-      <c r="B60" s="196"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="233">
+      <c r="B63" s="202"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="174">
         <v>140000</v>
       </c>
-      <c r="E60" s="147" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="119" t="s">
-        <v>177</v>
-      </c>
-      <c r="B61" s="115"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="233">
-        <v>85000</v>
-      </c>
-      <c r="E61" s="147" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="29" t="s">
+      <c r="E63" s="146" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="34"/>
-      <c r="C62" s="34"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="113">
-        <f>SUM(D52:D61)</f>
-        <v>722312.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="34" t="s">
+      <c r="B64" s="34"/>
+      <c r="C64" s="34"/>
+      <c r="D64" s="33"/>
+      <c r="E64" s="112">
+        <f>SUM(D55:D63)</f>
+        <v>705500</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B63" s="59"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="168"/>
-      <c r="E63" s="112"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
+      <c r="B65" s="59"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="166"/>
+      <c r="E65" s="111"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="176">
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="174">
         <v>57500</v>
       </c>
-      <c r="E64" s="114"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
+      <c r="E66" s="113"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="176">
-        <f>600+69416.74</f>
-        <v>70016.740000000005</v>
-      </c>
-      <c r="E65" s="39"/>
-    </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" s="50"/>
-      <c r="C66" s="50"/>
-      <c r="D66" s="74"/>
-      <c r="E66" s="68">
-        <f>SUM(D64:D65)</f>
-        <v>127516.74</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
-      <c r="D67" s="67"/>
-      <c r="E67" s="75"/>
-    </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="30" t="s">
+      <c r="D67" s="174">
+        <v>74836.23</v>
+      </c>
+      <c r="E67" s="39"/>
+    </row>
+    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" s="50"/>
+      <c r="C68" s="50"/>
+      <c r="D68" s="74"/>
+      <c r="E68" s="68">
+        <f>SUM(D66:D67)</f>
+        <v>132336.22999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="75"/>
+    </row>
+    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="B68" s="30"/>
-      <c r="C68" s="30"/>
-      <c r="D68" s="76"/>
-      <c r="E68" s="77"/>
-    </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="1"/>
-      <c r="D69" s="78"/>
-      <c r="E69" s="79"/>
-      <c r="F69" s="42"/>
-    </row>
-    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="76"/>
+      <c r="E70" s="77"/>
+    </row>
+    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1"/>
+      <c r="D71" s="78"/>
+      <c r="E71" s="79"/>
+      <c r="F71" s="42"/>
+    </row>
+    <row r="72" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B70" s="9"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="80"/>
-      <c r="E70" s="81">
-        <f>(SUM(E28:E68))</f>
-        <v>3891209.22</v>
-      </c>
-      <c r="F70" s="101"/>
-      <c r="G70" s="42"/>
-      <c r="H70" s="89"/>
-      <c r="I70" s="89"/>
-      <c r="J70" s="89"/>
-      <c r="K70" s="89"/>
-      <c r="L70" s="89"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D71" s="78"/>
-      <c r="E71" s="78"/>
-      <c r="H71" s="89"/>
-      <c r="I71" s="89"/>
-      <c r="J71" s="89"/>
-      <c r="K71" s="89"/>
-      <c r="L71" s="89"/>
-    </row>
-    <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D72" s="78"/>
-      <c r="E72" s="78"/>
-      <c r="H72" s="121"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="10" t="s">
+      <c r="B72" s="9"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="80"/>
+      <c r="E72" s="81">
+        <f>(SUM(E28:E70))</f>
+        <v>4500130.2699999996</v>
+      </c>
+      <c r="F72" s="101"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="89"/>
+      <c r="I72" s="89"/>
+      <c r="J72" s="89"/>
+      <c r="K72" s="89"/>
+      <c r="L72" s="89"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D73" s="78"/>
+      <c r="E73" s="78"/>
+      <c r="H73" s="89"/>
+      <c r="I73" s="89"/>
+      <c r="J73" s="89"/>
+      <c r="K73" s="89"/>
+      <c r="L73" s="89"/>
+    </row>
+    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D74" s="78"/>
+      <c r="E74" s="78"/>
+      <c r="H74" s="120"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B73" s="11"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="82"/>
-      <c r="E73" s="83"/>
-    </row>
-    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="195"/>
-      <c r="B74" s="196"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="93"/>
-      <c r="E74" s="69"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="195"/>
-      <c r="B75" s="196"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="71"/>
-      <c r="E75" s="69"/>
-    </row>
-    <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="11"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="82"/>
+      <c r="E75" s="83"/>
+    </row>
+    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="201"/>
       <c r="B76" s="202"/>
       <c r="C76" s="5"/>
-      <c r="D76" s="71"/>
+      <c r="D76" s="93"/>
       <c r="E76" s="69"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="70"/>
-      <c r="B77" s="72"/>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="201"/>
+      <c r="B77" s="202"/>
       <c r="C77" s="5"/>
       <c r="D77" s="71"/>
       <c r="E77" s="69"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="48"/>
-      <c r="B78" s="47"/>
-      <c r="C78" s="47"/>
-      <c r="D78" s="55"/>
-      <c r="E78" s="55">
-        <f>SUM(D74:D77)</f>
+    <row r="78" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="207"/>
+      <c r="B78" s="208"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="71"/>
+      <c r="E78" s="69"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="70"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="71"/>
+      <c r="E79" s="69"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="48"/>
+      <c r="B80" s="47"/>
+      <c r="C80" s="47"/>
+      <c r="D80" s="55"/>
+      <c r="E80" s="55">
+        <f>SUM(D76:D79)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="150" t="s">
+    <row r="81" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="149" t="s">
         <v>19</v>
       </c>
-      <c r="B81" s="151"/>
-      <c r="C81" s="151"/>
-      <c r="D81" s="152"/>
-      <c r="E81" s="153"/>
-    </row>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="3" t="s">
+      <c r="B83" s="150"/>
+      <c r="C83" s="150"/>
+      <c r="D83" s="151"/>
+      <c r="E83" s="152">
+        <v>801500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B83" s="9"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="60">
-        <f>E78+E81</f>
+      <c r="B85" s="9"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="60">
+        <f>E80+E83</f>
+        <v>801500</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="B87" s="66">
+        <f>E72</f>
+        <v>4500130.2699999996</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" s="66">
+        <f>E72-E70</f>
+        <v>4500130.2699999996</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="B89" s="66">
+        <f>E85-E83</f>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="65" t="s">
-        <v>13</v>
-      </c>
-      <c r="B85" s="66">
-        <f>E70</f>
-        <v>3891209.22</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="65" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" s="66">
-        <f>E70-E68</f>
-        <v>3891209.22</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="B87" s="66">
-        <f>E83-E81</f>
+    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B90" s="66">
+        <f>E85</f>
+        <v>801500</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="209"/>
+      <c r="B93" s="209"/>
+      <c r="C93" s="209"/>
+      <c r="D93" s="209"/>
+      <c r="E93" s="209"/>
+    </row>
+    <row r="94" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="209"/>
+      <c r="B94" s="209"/>
+      <c r="C94" s="209"/>
+      <c r="D94" s="209"/>
+      <c r="E94" s="209"/>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="209"/>
+      <c r="B95" s="209"/>
+      <c r="C95" s="209"/>
+      <c r="D95" s="209"/>
+      <c r="E95" s="209"/>
+    </row>
+    <row r="97" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="22"/>
+      <c r="B97" s="90"/>
+      <c r="C97" s="23"/>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="32"/>
+      <c r="B98" s="56">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="65" t="s">
-        <v>37</v>
-      </c>
-      <c r="B88" s="66">
-        <f>E83</f>
+      <c r="C98" s="25"/>
+    </row>
+    <row r="99" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" s="39">
+        <f>PRORRATEO!G34</f>
+        <v>4494340.58</v>
+      </c>
+      <c r="C99" s="23"/>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="24"/>
+      <c r="B100" s="39">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="203"/>
-      <c r="B91" s="203"/>
-      <c r="C91" s="203"/>
-      <c r="D91" s="203"/>
-      <c r="E91" s="203"/>
-    </row>
-    <row r="92" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="203"/>
-      <c r="B92" s="203"/>
-      <c r="C92" s="203"/>
-      <c r="D92" s="203"/>
-      <c r="E92" s="203"/>
-    </row>
-    <row r="93" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="203"/>
-      <c r="B93" s="203"/>
-      <c r="C93" s="203"/>
-      <c r="D93" s="203"/>
-      <c r="E93" s="203"/>
-    </row>
-    <row r="95" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="22"/>
-      <c r="B95" s="90"/>
-      <c r="C95" s="23"/>
-    </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="32"/>
-      <c r="B96" s="56">
+      <c r="C100" s="23"/>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B101" s="73">
+        <f>B127</f>
         <v>0</v>
       </c>
-      <c r="C96" s="25"/>
-    </row>
-    <row r="97" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B97" s="39">
+      <c r="C101" s="23"/>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="27"/>
+      <c r="B102" s="46"/>
+      <c r="C102" s="23"/>
+    </row>
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B103" s="46"/>
+      <c r="C103" s="23"/>
+    </row>
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B104" s="46">
+        <f>-B88</f>
+        <v>-4500130.2699999996</v>
+      </c>
+      <c r="C104" s="23"/>
+    </row>
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B105" s="46">
+        <f>-(B89)</f>
+        <v>0</v>
+      </c>
+      <c r="C105" s="23"/>
+    </row>
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" s="56">
+        <f>SUM(B98:B105)</f>
+        <v>-5789.6899999994785</v>
+      </c>
+      <c r="C106" s="26"/>
+      <c r="D106" s="42"/>
+    </row>
+    <row r="107" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="40"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="42"/>
+      <c r="E107" s="91"/>
+      <c r="F107" s="92"/>
+    </row>
+    <row r="108" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="41"/>
+      <c r="C108" s="26"/>
+    </row>
+    <row r="109" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109"/>
+      <c r="B109" s="40"/>
+      <c r="C109" s="36"/>
+    </row>
+    <row r="110" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="95" t="s">
+        <v>132</v>
+      </c>
+      <c r="B110" s="148">
+        <v>5539308.3700000001</v>
+      </c>
+      <c r="C110" s="36"/>
+      <c r="D110" s="45"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="B111" s="161">
+        <f>-B88</f>
+        <v>-4500130.2699999996</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B112" s="99">
+        <f>-B89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="B113" s="161">
+        <v>-76800</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="B114" s="99">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A115" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="B115" s="161">
+        <v>-231879</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="B116" s="161">
+        <v>-6754</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="B117" s="161">
+        <v>-116717.02</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B118" s="99">
+        <f>B127</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="B119" s="100">
         <f>PRORRATEO!G34</f>
-        <v>4405361.22</v>
-      </c>
-      <c r="C97" s="23"/>
-    </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="24"/>
-      <c r="B98" s="39">
+        <v>4494340.58</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="B120" s="98">
+        <f>SUM(B110:C119)</f>
+        <v>5421368.6600000001</v>
+      </c>
+      <c r="D120" s="42"/>
+      <c r="E120" s="42"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="96"/>
+      <c r="B121" s="96"/>
+    </row>
+    <row r="122" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="210" t="s">
+        <v>30</v>
+      </c>
+      <c r="B123" s="210"/>
+      <c r="C123" s="210"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="210"/>
+      <c r="B124" s="210"/>
+      <c r="C124" s="210"/>
+    </row>
+    <row r="125" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="85"/>
+      <c r="B125" s="35">
         <v>0</v>
       </c>
-      <c r="C98" s="23"/>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B99" s="73">
-        <f>B123</f>
-        <v>231879</v>
-      </c>
-      <c r="C99" s="23"/>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="27"/>
-      <c r="B100" s="46"/>
-      <c r="C100" s="23"/>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="B101" s="46"/>
-      <c r="C101" s="23"/>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B102" s="46">
-        <f>-B86</f>
-        <v>-3891209.22</v>
-      </c>
-      <c r="C102" s="23"/>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B103" s="46">
-        <f>-(B87)</f>
+      <c r="C125" s="35">
+        <v>40000</v>
+      </c>
+      <c r="E125" s="101"/>
+    </row>
+    <row r="126" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="85"/>
+      <c r="B126" s="87"/>
+      <c r="C126" s="84"/>
+      <c r="D126" s="101"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" s="86">
+        <f>SUM(B125:B126)</f>
         <v>0</v>
       </c>
-      <c r="C103" s="23"/>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B104" s="56">
-        <f>SUM(B96:B103)</f>
-        <v>746030.99999999953</v>
-      </c>
-      <c r="C104" s="26"/>
-      <c r="D104" s="42"/>
-    </row>
-    <row r="105" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="40"/>
-      <c r="C105" s="26"/>
-      <c r="D105" s="42"/>
-      <c r="E105" s="91"/>
-      <c r="F105" s="92"/>
-    </row>
-    <row r="106" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="41"/>
-      <c r="C106" s="26"/>
-    </row>
-    <row r="107" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107"/>
-      <c r="B107" s="40"/>
-      <c r="C107" s="36"/>
-    </row>
-    <row r="108" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="95" t="s">
-        <v>137</v>
-      </c>
-      <c r="B108" s="149">
-        <v>4494193.4000000004</v>
-      </c>
-      <c r="C108" s="36"/>
-      <c r="D108" s="45"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="B109" s="162">
-        <f>-B86</f>
-        <v>-3891209.22</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B110" s="99">
-        <f>-B87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A111" s="52" t="s">
-        <v>158</v>
-      </c>
-      <c r="B111" s="162">
-        <v>-141652</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="52" t="s">
-        <v>159</v>
-      </c>
-      <c r="B112" s="162">
-        <v>-300000</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="B113" s="99">
-        <v>320000</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="B114" s="99">
-        <f>B123</f>
-        <v>231879</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="B115" s="100">
-        <f>PRORRATEO!G34</f>
-        <v>4405361.22</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="97" t="s">
-        <v>44</v>
-      </c>
-      <c r="B116" s="98">
-        <f>SUM(B108:C115)</f>
-        <v>5118572.4000000004</v>
-      </c>
-      <c r="D116" s="42"/>
-      <c r="E116" s="42"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="96"/>
-      <c r="B117" s="96"/>
-    </row>
-    <row r="118" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="204" t="s">
-        <v>30</v>
-      </c>
-      <c r="B119" s="204"/>
-      <c r="C119" s="204"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="204"/>
-      <c r="B120" s="204"/>
-      <c r="C120" s="204"/>
-    </row>
-    <row r="121" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="85" t="s">
-        <v>160</v>
-      </c>
-      <c r="B121" s="35">
-        <v>231879</v>
-      </c>
-      <c r="C121" s="35">
-        <v>40000</v>
-      </c>
-      <c r="E121" s="101"/>
-    </row>
-    <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="85"/>
-      <c r="B122" s="87"/>
-      <c r="C122" s="84"/>
-      <c r="D122" s="101"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B123" s="86">
-        <f>SUM(B121:B122)</f>
-        <v>231879</v>
-      </c>
-      <c r="C123" s="44"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M124" s="7"/>
-    </row>
-    <row r="125" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="203"/>
-      <c r="B125" s="203"/>
-      <c r="C125" s="203"/>
-      <c r="D125" s="203"/>
-      <c r="E125" s="203"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A126" s="203"/>
-      <c r="B126" s="203"/>
-      <c r="C126" s="203"/>
-      <c r="D126" s="203"/>
-      <c r="E126" s="203"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A127" s="203"/>
-      <c r="B127" s="203"/>
-      <c r="C127" s="203"/>
-      <c r="D127" s="203"/>
-      <c r="E127" s="203"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A128" s="203"/>
-      <c r="B128" s="203"/>
-      <c r="C128" s="203"/>
-      <c r="D128" s="203"/>
-      <c r="E128" s="203"/>
+      <c r="C127" s="44"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M128" s="7"/>
+    </row>
+    <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="209"/>
+      <c r="B129" s="209"/>
+      <c r="C129" s="209"/>
+      <c r="D129" s="209"/>
+      <c r="E129" s="209"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="209"/>
+      <c r="B130" s="209"/>
+      <c r="C130" s="209"/>
+      <c r="D130" s="209"/>
+      <c r="E130" s="209"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="209"/>
+      <c r="B131" s="209"/>
+      <c r="C131" s="209"/>
+      <c r="D131" s="209"/>
+      <c r="E131" s="209"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="209"/>
+      <c r="B132" s="209"/>
+      <c r="C132" s="209"/>
+      <c r="D132" s="209"/>
+      <c r="E132" s="209"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A125:E128"/>
-    <mergeCell ref="A119:C120"/>
-    <mergeCell ref="A91:E93"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A129:E132"/>
+    <mergeCell ref="A123:C124"/>
+    <mergeCell ref="A93:E95"/>
+    <mergeCell ref="A77:B77"/>
     <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A78:B78"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A49:B49"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B1:D1"/>
@@ -3180,51 +3267,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="212"/>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
+      <c r="E1" s="218"/>
+      <c r="F1" s="218"/>
+      <c r="G1" s="218"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="218"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="218"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F2" s="6"/>
-      <c r="G2" s="120">
+      <c r="G2" s="119">
         <v>801500</v>
       </c>
       <c r="H2" s="6"/>
@@ -3232,14 +3319,14 @@
       <c r="J2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="154">
+      <c r="K2" s="153">
         <v>3155000</v>
       </c>
       <c r="L2" s="94"/>
       <c r="M2" s="53"/>
       <c r="N2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3254,156 +3341,156 @@
       <c r="L3" s="57"/>
       <c r="M3" s="57"/>
     </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="219" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="220"/>
-      <c r="C4" s="220"/>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
-      <c r="M4" s="221"/>
-    </row>
-    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="222"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="194"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="194"/>
-      <c r="I5" s="194"/>
-      <c r="J5" s="194"/>
-      <c r="K5" s="194"/>
-      <c r="L5" s="194"/>
-      <c r="M5" s="223"/>
-    </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="224"/>
-      <c r="B6" s="225"/>
-      <c r="C6" s="225"/>
-      <c r="D6" s="225"/>
-      <c r="E6" s="225"/>
-      <c r="F6" s="225"/>
-      <c r="G6" s="225"/>
-      <c r="H6" s="225"/>
-      <c r="I6" s="225"/>
-      <c r="J6" s="225"/>
-      <c r="K6" s="225"/>
-      <c r="L6" s="225"/>
-      <c r="M6" s="226"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="205" t="s">
+    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="225" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="226"/>
+      <c r="C4" s="226"/>
+      <c r="D4" s="226"/>
+      <c r="E4" s="226"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="226"/>
+      <c r="H4" s="226"/>
+      <c r="I4" s="226"/>
+      <c r="J4" s="226"/>
+      <c r="K4" s="226"/>
+      <c r="L4" s="226"/>
+      <c r="M4" s="227"/>
+    </row>
+    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="228"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="200"/>
+      <c r="F5" s="200"/>
+      <c r="G5" s="200"/>
+      <c r="H5" s="200"/>
+      <c r="I5" s="200"/>
+      <c r="J5" s="200"/>
+      <c r="K5" s="200"/>
+      <c r="L5" s="200"/>
+      <c r="M5" s="229"/>
+    </row>
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="230"/>
+      <c r="B6" s="231"/>
+      <c r="C6" s="231"/>
+      <c r="D6" s="231"/>
+      <c r="E6" s="231"/>
+      <c r="F6" s="231"/>
+      <c r="G6" s="231"/>
+      <c r="H6" s="231"/>
+      <c r="I6" s="231"/>
+      <c r="J6" s="231"/>
+      <c r="K6" s="231"/>
+      <c r="L6" s="231"/>
+      <c r="M6" s="232"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="205" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="205" t="s">
+      <c r="B7" s="211" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="205" t="s">
+      <c r="D7" s="211" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="205" t="s">
+      <c r="E7" s="211" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="213" t="s">
+      <c r="F7" s="219" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="205" t="s">
+      <c r="G7" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="215" t="s">
+      <c r="H7" s="221" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="213" t="s">
+      <c r="I7" s="219" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="213" t="s">
+      <c r="J7" s="219" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="217" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" s="155" t="s">
+      <c r="K7" s="223" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="211" t="s">
+      <c r="M7" s="217" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="205"/>
-      <c r="B8" s="206"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="206"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="214"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="216"/>
-      <c r="I8" s="214"/>
-      <c r="J8" s="214"/>
-      <c r="K8" s="218"/>
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="211"/>
+      <c r="B8" s="212"/>
+      <c r="C8" s="211"/>
+      <c r="D8" s="212"/>
+      <c r="E8" s="211"/>
+      <c r="F8" s="220"/>
+      <c r="G8" s="211"/>
+      <c r="H8" s="222"/>
+      <c r="I8" s="220"/>
+      <c r="J8" s="220"/>
+      <c r="K8" s="224"/>
       <c r="L8" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/05</v>
       </c>
-      <c r="M8" s="211"/>
-    </row>
-    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="123">
+      <c r="M8" s="217"/>
+    </row>
+    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="122">
         <v>1</v>
       </c>
-      <c r="B9" s="123" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="123" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="123" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" s="145">
+      <c r="B9" s="122" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="122" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="122" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="144">
         <v>3.43</v>
       </c>
-      <c r="F9" s="125">
+      <c r="F9" s="124">
         <v>135708.01</v>
       </c>
-      <c r="G9" s="134">
+      <c r="G9" s="133">
         <f>F9</f>
         <v>135708.01</v>
       </c>
-      <c r="H9" s="126">
+      <c r="H9" s="125">
         <f t="shared" ref="H9:H33" si="0">F9-G9</f>
         <v>0</v>
       </c>
-      <c r="I9" s="126">
+      <c r="I9" s="125">
         <f>IF(H9&gt;0,H9*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="127">
+      <c r="J9" s="126">
         <f>K$2*E9%</f>
         <v>108216.50000000001</v>
       </c>
-      <c r="K9" s="128">
+      <c r="K9" s="127">
         <f>G$2*E9/100</f>
         <v>27491.45</v>
       </c>
-      <c r="L9" s="129">
+      <c r="L9" s="128">
         <f t="shared" ref="L9:L33" si="1">ROUND(SUM(H9:K9),0) + N9</f>
         <v>135708.01</v>
       </c>
-      <c r="M9" s="130">
+      <c r="M9" s="129">
         <f t="shared" ref="M9:M33" si="2">ROUND(L9*3%,0) + L9</f>
         <v>139779.01</v>
       </c>
@@ -3411,52 +3498,53 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="234">
+    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="131">
         <f>A9+1</f>
         <v>2</v>
       </c>
-      <c r="B10" s="234" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="234" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="235" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="146">
+      <c r="B10" s="131" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="131" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="132" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="145">
         <v>2.95</v>
       </c>
-      <c r="F10" s="134">
-        <v>262617.02</v>
-      </c>
-      <c r="G10" s="134">
-        <v>141652</v>
-      </c>
-      <c r="H10" s="126">
+      <c r="F10" s="133">
+        <v>241311.02</v>
+      </c>
+      <c r="G10" s="133">
+        <f>124594+116717.02</f>
+        <v>241311.02000000002</v>
+      </c>
+      <c r="H10" s="125">
         <f t="shared" si="0"/>
-        <v>120965.02000000002</v>
-      </c>
-      <c r="I10" s="126">
+        <v>0</v>
+      </c>
+      <c r="I10" s="125">
         <f t="shared" ref="I10:I33" si="3">IF(H10&gt;0,H10*3%,0)</f>
-        <v>3628.9506000000006</v>
-      </c>
-      <c r="J10" s="127">
+        <v>0</v>
+      </c>
+      <c r="J10" s="126">
         <f t="shared" ref="J10:J32" si="4">K$2*E10%</f>
         <v>93072.5</v>
       </c>
-      <c r="K10" s="128">
+      <c r="K10" s="127">
         <f t="shared" ref="K10:K32" si="5">G$2*E10/100</f>
         <v>23644.25</v>
       </c>
-      <c r="L10" s="129">
+      <c r="L10" s="128">
         <f t="shared" si="1"/>
-        <v>241311.02</v>
-      </c>
-      <c r="M10" s="130">
+        <v>116717.02</v>
+      </c>
+      <c r="M10" s="129">
         <f t="shared" si="2"/>
-        <v>248550.02</v>
+        <v>120219.02</v>
       </c>
       <c r="N10" s="42">
         <f>N9+0.01</f>
@@ -3464,109 +3552,106 @@
       </c>
       <c r="O10" s="42"/>
     </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="132">
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="131">
         <f t="shared" ref="A11:A32" si="6">A10+1</f>
         <v>3</v>
       </c>
-      <c r="B11" s="132" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="132" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="133" t="s">
-        <v>141</v>
-      </c>
-      <c r="E11" s="146">
+      <c r="B11" s="131" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="131" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="132" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="145">
         <f>5.78+1.02</f>
         <v>6.8000000000000007</v>
       </c>
-      <c r="F11" s="134">
+      <c r="F11" s="133">
         <v>269042.03000000003</v>
       </c>
-      <c r="G11" s="134">
-        <f>F11</f>
-        <v>269042.03000000003</v>
-      </c>
-      <c r="H11" s="126">
+      <c r="G11" s="133">
+        <v>277113.03000000003</v>
+      </c>
+      <c r="H11" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="126">
+        <v>-8071</v>
+      </c>
+      <c r="I11" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="126">
         <f t="shared" si="4"/>
         <v>214540.00000000003</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="127">
         <f t="shared" si="5"/>
         <v>54502.000000000007</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="128">
         <f t="shared" si="1"/>
-        <v>269042.03000000003</v>
-      </c>
-      <c r="M11" s="130">
+        <v>260971.03</v>
+      </c>
+      <c r="M11" s="129">
         <f t="shared" si="2"/>
-        <v>277113.03000000003</v>
+        <v>268800.03000000003</v>
       </c>
       <c r="N11" s="42">
         <f t="shared" ref="N11:N33" si="7">N10+0.01</f>
         <v>0.03</v>
       </c>
       <c r="O11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="123">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="122">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="B12" s="123" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="123" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="131" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" s="145">
+      <c r="B12" s="122" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="130"/>
+      <c r="E12" s="144">
         <v>3.43</v>
       </c>
-      <c r="F12" s="125">
-        <v>135708.04</v>
-      </c>
-      <c r="G12" s="134">
-        <v>139779.04</v>
-      </c>
-      <c r="H12" s="126">
+      <c r="F12" s="124">
+        <v>131637.04</v>
+      </c>
+      <c r="G12" s="133">
+        <v>135586.04</v>
+      </c>
+      <c r="H12" s="125">
         <f t="shared" si="0"/>
-        <v>-4071</v>
-      </c>
-      <c r="I12" s="126">
+        <v>-3949</v>
+      </c>
+      <c r="I12" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J12" s="127">
+      <c r="J12" s="126">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K12" s="128">
+      <c r="K12" s="127">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L12" s="129">
+      <c r="L12" s="128">
         <f t="shared" si="1"/>
-        <v>131637.04</v>
-      </c>
-      <c r="M12" s="130">
+        <v>131759.04000000001</v>
+      </c>
+      <c r="M12" s="129">
         <f t="shared" si="2"/>
-        <v>135586.04</v>
+        <v>135712.04</v>
       </c>
       <c r="N12" s="42">
         <f t="shared" si="7"/>
@@ -3574,49 +3659,49 @@
       </c>
       <c r="P12" s="42"/>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="123">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="122">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="B13" s="123" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="123" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="131"/>
-      <c r="E13" s="145">
+      <c r="B13" s="122" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="122" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="130"/>
+      <c r="E13" s="144">
         <v>2.95</v>
       </c>
-      <c r="F13" s="125">
+      <c r="F13" s="124">
         <v>116717.05</v>
       </c>
-      <c r="G13" s="134">
+      <c r="G13" s="133">
         <f>F13</f>
         <v>116717.05</v>
       </c>
-      <c r="H13" s="126">
+      <c r="H13" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="126">
+      <c r="I13" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J13" s="127">
+      <c r="J13" s="126">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K13" s="128">
+      <c r="K13" s="127">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L13" s="129">
+      <c r="L13" s="128">
         <f t="shared" si="1"/>
         <v>116717.05</v>
       </c>
-      <c r="M13" s="130">
+      <c r="M13" s="129">
         <f t="shared" si="2"/>
         <v>120219.05</v>
       </c>
@@ -3626,97 +3711,103 @@
       </c>
       <c r="P13" s="42"/>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="187">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="131">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="B14" s="187" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="187" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="187"/>
-      <c r="E14" s="145">
+      <c r="B14" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="131" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="131"/>
+      <c r="E14" s="144">
         <v>5.69</v>
       </c>
-      <c r="F14" s="125">
-        <v>225125.06</v>
-      </c>
-      <c r="G14" s="134"/>
-      <c r="H14" s="126">
+      <c r="F14" s="124">
+        <v>457004.06</v>
+      </c>
+      <c r="G14" s="133">
+        <f>231879+218371.06+6754</f>
+        <v>457004.06</v>
+      </c>
+      <c r="H14" s="125">
         <f t="shared" si="0"/>
-        <v>225125.06</v>
-      </c>
-      <c r="I14" s="126">
+        <v>0</v>
+      </c>
+      <c r="I14" s="125">
         <f t="shared" si="3"/>
-        <v>6753.7518</v>
-      </c>
-      <c r="J14" s="127">
+        <v>0</v>
+      </c>
+      <c r="J14" s="126">
         <f t="shared" si="4"/>
         <v>179519.50000000003</v>
       </c>
-      <c r="K14" s="128">
+      <c r="K14" s="127">
         <f t="shared" si="5"/>
         <v>45605.35</v>
       </c>
-      <c r="L14" s="129">
+      <c r="L14" s="128">
         <f t="shared" si="1"/>
-        <v>457004.06</v>
-      </c>
-      <c r="M14" s="130">
+        <v>225125.06</v>
+      </c>
+      <c r="M14" s="129">
         <f t="shared" si="2"/>
-        <v>470714.06</v>
+        <v>231879.06</v>
       </c>
       <c r="N14" s="42">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="123">
+      <c r="O14" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="122">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="B15" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="123" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="123"/>
-      <c r="E15" s="145">
+      <c r="B15" s="122" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="122" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="122"/>
+      <c r="E15" s="144">
         <v>3.43</v>
       </c>
-      <c r="F15" s="125">
+      <c r="F15" s="124">
         <v>139779.07</v>
       </c>
-      <c r="G15" s="134">
+      <c r="G15" s="133">
         <f>F15</f>
         <v>139779.07</v>
       </c>
-      <c r="H15" s="126">
+      <c r="H15" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="126">
+      <c r="I15" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="127">
+      <c r="J15" s="126">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K15" s="128">
+      <c r="K15" s="127">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L15" s="129">
+      <c r="L15" s="128">
         <f t="shared" si="1"/>
         <v>135708.07</v>
       </c>
-      <c r="M15" s="130">
+      <c r="M15" s="129">
         <f t="shared" si="2"/>
         <v>139779.07</v>
       </c>
@@ -3724,102 +3815,108 @@
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="123">
+      <c r="O15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="122">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="B16" s="123" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="123" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="131" t="s">
-        <v>157</v>
-      </c>
-      <c r="E16" s="145">
+      <c r="B16" s="122" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="122" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="130" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="144">
         <v>2.95</v>
       </c>
-      <c r="F16" s="125">
-        <v>262617.08</v>
-      </c>
-      <c r="G16" s="134"/>
-      <c r="H16" s="126">
+      <c r="F16" s="124">
+        <v>387212.08</v>
+      </c>
+      <c r="G16" s="133">
+        <f>F16</f>
+        <v>387212.08</v>
+      </c>
+      <c r="H16" s="125">
         <f t="shared" si="0"/>
-        <v>262617.08</v>
-      </c>
-      <c r="I16" s="126">
+        <v>0</v>
+      </c>
+      <c r="I16" s="125">
         <f t="shared" si="3"/>
-        <v>7878.5124000000005</v>
-      </c>
-      <c r="J16" s="127">
+        <v>0</v>
+      </c>
+      <c r="J16" s="126">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K16" s="128">
+      <c r="K16" s="127">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L16" s="129">
+      <c r="L16" s="128">
         <f t="shared" si="1"/>
-        <v>387212.08</v>
-      </c>
-      <c r="M16" s="130">
+        <v>116717.08</v>
+      </c>
+      <c r="M16" s="129">
         <f t="shared" si="2"/>
-        <v>398828.08</v>
+        <v>120219.08</v>
       </c>
       <c r="N16" s="42">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="123">
+    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="122">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="B17" s="123" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="123" t="s">
-        <v>127</v>
-      </c>
-      <c r="D17" s="131" t="s">
-        <v>124</v>
-      </c>
-      <c r="E17" s="145">
+      <c r="B17" s="122" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="122" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="130" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="144">
         <v>5.69</v>
       </c>
-      <c r="F17" s="125">
+      <c r="F17" s="124">
         <v>225125.09</v>
       </c>
-      <c r="G17" s="134">
+      <c r="G17" s="133">
         <f>F17</f>
         <v>225125.09</v>
       </c>
-      <c r="H17" s="126">
+      <c r="H17" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="126">
+      <c r="I17" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="127">
+      <c r="J17" s="126">
         <f t="shared" si="4"/>
         <v>179519.50000000003</v>
       </c>
-      <c r="K17" s="128">
+      <c r="K17" s="127">
         <f t="shared" si="5"/>
         <v>45605.35</v>
       </c>
-      <c r="L17" s="129">
+      <c r="L17" s="128">
         <f t="shared" si="1"/>
         <v>225125.09</v>
       </c>
-      <c r="M17" s="130">
+      <c r="M17" s="129">
         <f t="shared" si="2"/>
         <v>231879.09</v>
       </c>
@@ -3828,208 +3925,208 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="123">
+    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="122">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="B18" s="123" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="123" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="131" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" s="145">
+      <c r="B18" s="122" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="130" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="144">
         <v>3.43</v>
       </c>
-      <c r="F18" s="125">
-        <v>135429.1</v>
-      </c>
-      <c r="G18" s="134">
+      <c r="F18" s="124">
+        <v>275200.09999999998</v>
+      </c>
+      <c r="G18" s="133">
         <v>0</v>
       </c>
-      <c r="H18" s="126">
+      <c r="H18" s="125">
         <f t="shared" si="0"/>
-        <v>135429.1</v>
-      </c>
-      <c r="I18" s="126">
+        <v>275200.09999999998</v>
+      </c>
+      <c r="I18" s="125">
         <f t="shared" si="3"/>
-        <v>4062.873</v>
-      </c>
-      <c r="J18" s="127">
+        <v>8256.0029999999988</v>
+      </c>
+      <c r="J18" s="126">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K18" s="128">
+      <c r="K18" s="127">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L18" s="129">
+      <c r="L18" s="128">
         <f t="shared" si="1"/>
-        <v>275200.09999999998</v>
-      </c>
-      <c r="M18" s="130">
+        <v>419164.1</v>
+      </c>
+      <c r="M18" s="129">
         <f t="shared" si="2"/>
-        <v>283456.09999999998</v>
+        <v>431739.1</v>
       </c>
       <c r="N18" s="42">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="123">
+    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="122">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="B19" s="123" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="123" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" s="131" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" s="145">
+      <c r="B19" s="122" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="122" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" s="144">
         <v>2.95</v>
       </c>
-      <c r="F19" s="125">
-        <v>116717.11</v>
-      </c>
-      <c r="G19" s="134">
-        <v>120220</v>
-      </c>
-      <c r="H19" s="126">
+      <c r="F19" s="124">
+        <v>113214.11</v>
+      </c>
+      <c r="G19" s="133">
+        <v>116610.11</v>
+      </c>
+      <c r="H19" s="125">
         <f t="shared" si="0"/>
-        <v>-3502.8899999999994</v>
-      </c>
-      <c r="I19" s="126">
+        <v>-3396</v>
+      </c>
+      <c r="I19" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J19" s="127">
+      <c r="J19" s="126">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K19" s="128">
+      <c r="K19" s="127">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L19" s="129">
+      <c r="L19" s="128">
         <f t="shared" si="1"/>
-        <v>113214.11</v>
-      </c>
-      <c r="M19" s="130">
+        <v>113321.11</v>
+      </c>
+      <c r="M19" s="129">
         <f t="shared" si="2"/>
-        <v>116610.11</v>
+        <v>116721.11</v>
       </c>
       <c r="N19" s="42">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="123">
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="122">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="B20" s="123" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" s="131" t="s">
-        <v>125</v>
-      </c>
-      <c r="E20" s="145">
+      <c r="B20" s="122" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="122" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="130" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="144">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F20" s="125">
+      <c r="F20" s="124">
+        <v>245303.12</v>
+      </c>
+      <c r="G20" s="133">
         <v>252662.12</v>
       </c>
-      <c r="G20" s="134">
-        <v>252662.12</v>
-      </c>
-      <c r="H20" s="126">
+      <c r="H20" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="126">
+        <v>-7359</v>
+      </c>
+      <c r="I20" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="127">
+      <c r="J20" s="126">
         <f t="shared" si="4"/>
         <v>195610</v>
       </c>
-      <c r="K20" s="128">
+      <c r="K20" s="127">
         <f t="shared" si="5"/>
         <v>49693</v>
       </c>
-      <c r="L20" s="129">
+      <c r="L20" s="128">
         <f t="shared" si="1"/>
-        <v>245303.12</v>
-      </c>
-      <c r="M20" s="130">
+        <v>237944.12</v>
+      </c>
+      <c r="M20" s="129">
         <f t="shared" si="2"/>
-        <v>252662.12</v>
+        <v>245082.12</v>
       </c>
       <c r="N20" s="42">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="123">
+    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="122">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="B21" s="123" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="123" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" s="131" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21" s="145">
+      <c r="B21" s="122" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="122" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="130" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="144">
         <v>3.43</v>
       </c>
-      <c r="F21" s="125">
+      <c r="F21" s="124">
         <v>135708.13</v>
       </c>
-      <c r="G21" s="134">
+      <c r="G21" s="133">
         <f>F21</f>
         <v>135708.13</v>
       </c>
-      <c r="H21" s="126">
+      <c r="H21" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="126">
+      <c r="I21" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="127">
+      <c r="J21" s="126">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K21" s="128">
+      <c r="K21" s="127">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L21" s="129">
+      <c r="L21" s="128">
         <f t="shared" si="1"/>
         <v>135708.13</v>
       </c>
-      <c r="M21" s="130">
+      <c r="M21" s="129">
         <f t="shared" si="2"/>
         <v>139779.13</v>
       </c>
@@ -4038,51 +4135,51 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="123">
+    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="122">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="B22" s="123" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="123" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="131" t="s">
-        <v>152</v>
-      </c>
-      <c r="E22" s="145">
+      <c r="B22" s="122" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="122" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="130" t="s">
+        <v>142</v>
+      </c>
+      <c r="E22" s="144">
         <v>2.95</v>
       </c>
-      <c r="F22" s="125">
+      <c r="F22" s="124">
         <v>116717.14</v>
       </c>
-      <c r="G22" s="134">
+      <c r="G22" s="133">
         <f>F22</f>
         <v>116717.14</v>
       </c>
-      <c r="H22" s="126">
+      <c r="H22" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="126">
+      <c r="I22" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J22" s="127">
+      <c r="J22" s="126">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K22" s="128">
+      <c r="K22" s="127">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L22" s="129">
+      <c r="L22" s="128">
         <f t="shared" si="1"/>
         <v>116717.14</v>
       </c>
-      <c r="M22" s="130">
+      <c r="M22" s="129">
         <f t="shared" si="2"/>
         <v>120219.14</v>
       </c>
@@ -4091,52 +4188,52 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="132">
+    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="131">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="B23" s="132" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="132" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="133" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" s="146">
+      <c r="B23" s="131" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="131" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="132" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="145">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F23" s="134">
-        <v>551941.15</v>
-      </c>
-      <c r="G23" s="134">
+      <c r="F23" s="133">
+        <v>245303.15</v>
+      </c>
+      <c r="G23" s="133">
         <f>F23</f>
-        <v>551941.15</v>
-      </c>
-      <c r="H23" s="126">
+        <v>245303.15</v>
+      </c>
+      <c r="H23" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="126">
+      <c r="I23" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J23" s="127">
+      <c r="J23" s="126">
         <f t="shared" si="4"/>
         <v>195610</v>
       </c>
-      <c r="K23" s="128">
+      <c r="K23" s="127">
         <f t="shared" si="5"/>
         <v>49693</v>
       </c>
-      <c r="L23" s="129">
+      <c r="L23" s="128">
         <f t="shared" si="1"/>
         <v>245303.15</v>
       </c>
-      <c r="M23" s="130">
+      <c r="M23" s="129">
         <f t="shared" si="2"/>
         <v>252662.15</v>
       </c>
@@ -4145,101 +4242,99 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="123">
+    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="122">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="B24" s="123" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="123" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="123"/>
-      <c r="E24" s="145">
+      <c r="B24" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="122" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="122"/>
+      <c r="E24" s="144">
         <v>3.43</v>
       </c>
-      <c r="F24" s="125">
-        <v>135708.16</v>
-      </c>
-      <c r="G24" s="134">
-        <v>139779.13</v>
-      </c>
-      <c r="H24" s="126">
+      <c r="F24" s="124">
+        <v>131637.16</v>
+      </c>
+      <c r="G24" s="133"/>
+      <c r="H24" s="125">
         <f t="shared" si="0"/>
-        <v>-4070.9700000000012</v>
-      </c>
-      <c r="I24" s="126">
+        <v>131637.16</v>
+      </c>
+      <c r="I24" s="125">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="127">
+        <v>3949.1147999999998</v>
+      </c>
+      <c r="J24" s="126">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K24" s="128">
+      <c r="K24" s="127">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L24" s="129">
+      <c r="L24" s="128">
         <f t="shared" si="1"/>
-        <v>131637.16</v>
-      </c>
-      <c r="M24" s="130">
+        <v>271294.15999999997</v>
+      </c>
+      <c r="M24" s="129">
         <f t="shared" si="2"/>
-        <v>135586.16</v>
+        <v>279433.15999999997</v>
       </c>
       <c r="N24" s="42">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="123">
+    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="122">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="B25" s="123" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="123" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" s="131" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" s="145">
+      <c r="B25" s="122" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="122" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="130" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="144">
         <v>2.95</v>
       </c>
-      <c r="F25" s="134">
-        <v>262617.17</v>
-      </c>
-      <c r="G25" s="134">
-        <f>120966+141651.17</f>
-        <v>262617.17000000004</v>
-      </c>
-      <c r="H25" s="126">
+      <c r="F25" s="133">
+        <v>116717.17</v>
+      </c>
+      <c r="G25" s="133">
+        <f>F25</f>
+        <v>116717.17</v>
+      </c>
+      <c r="H25" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I25" s="126">
+      <c r="I25" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="127">
+      <c r="J25" s="126">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K25" s="128">
+      <c r="K25" s="127">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L25" s="129">
+      <c r="L25" s="128">
         <f t="shared" si="1"/>
         <v>116717.17</v>
       </c>
-      <c r="M25" s="130">
+      <c r="M25" s="129">
         <f t="shared" si="2"/>
         <v>120219.17</v>
       </c>
@@ -4248,154 +4343,153 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="132">
+    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="131">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="B26" s="132" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" s="132" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="156"/>
-      <c r="E26" s="146">
+      <c r="B26" s="131" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="131" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" s="155"/>
+      <c r="E26" s="145">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F26" s="134">
-        <v>245303.18</v>
-      </c>
-      <c r="G26" s="134">
-        <v>252662.18</v>
-      </c>
-      <c r="H26" s="126">
+      <c r="F26" s="133">
+        <v>237944.18</v>
+      </c>
+      <c r="G26" s="133">
+        <f>F26</f>
+        <v>237944.18</v>
+      </c>
+      <c r="H26" s="125">
         <f t="shared" si="0"/>
-        <v>-7359</v>
-      </c>
-      <c r="I26" s="126">
+        <v>0</v>
+      </c>
+      <c r="I26" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="127">
+      <c r="J26" s="126">
         <f t="shared" si="4"/>
         <v>195610</v>
       </c>
-      <c r="K26" s="128">
+      <c r="K26" s="127">
         <f t="shared" si="5"/>
         <v>49693</v>
       </c>
-      <c r="L26" s="129">
+      <c r="L26" s="128">
         <f t="shared" si="1"/>
-        <v>237944.18</v>
-      </c>
-      <c r="M26" s="130">
+        <v>245303.18</v>
+      </c>
+      <c r="M26" s="129">
         <f t="shared" si="2"/>
-        <v>245082.18</v>
+        <v>252662.18</v>
       </c>
       <c r="N26" s="42">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="132">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="131">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="B27" s="132" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="132" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="133" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" s="146">
+      <c r="B27" s="131" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="131" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="132" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" s="145">
         <v>3.43</v>
       </c>
-      <c r="F27" s="134">
-        <f>149147.19+141652</f>
-        <v>290799.19</v>
-      </c>
-      <c r="G27" s="163">
-        <v>116717.02</v>
-      </c>
-      <c r="H27" s="126">
+      <c r="F27" s="133">
+        <v>315013.19</v>
+      </c>
+      <c r="G27" s="198"/>
+      <c r="H27" s="125">
         <f t="shared" si="0"/>
-        <v>174082.16999999998</v>
-      </c>
-      <c r="I27" s="126">
+        <v>315013.19</v>
+      </c>
+      <c r="I27" s="125">
         <f t="shared" si="3"/>
-        <v>5222.4650999999994</v>
-      </c>
-      <c r="J27" s="127">
+        <v>9450.3956999999991</v>
+      </c>
+      <c r="J27" s="126">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K27" s="128">
+      <c r="K27" s="127">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L27" s="129">
+      <c r="L27" s="128">
         <f t="shared" si="1"/>
-        <v>315013.19</v>
-      </c>
-      <c r="M27" s="130">
+        <v>460172.19</v>
+      </c>
+      <c r="M27" s="129">
         <f t="shared" si="2"/>
-        <v>324463.19</v>
+        <v>473977.19</v>
       </c>
       <c r="N27" s="42">
         <f t="shared" si="7"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="132">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="131">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="B28" s="157" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="132" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28" s="133" t="s">
-        <v>154</v>
-      </c>
-      <c r="E28" s="146">
+      <c r="B28" s="156" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="131" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="132" t="s">
+        <v>144</v>
+      </c>
+      <c r="E28" s="145">
         <v>2.95</v>
       </c>
-      <c r="F28" s="136">
-        <v>258369.4</v>
-      </c>
-      <c r="G28" s="136">
-        <v>258369.4</v>
-      </c>
-      <c r="H28" s="126">
+      <c r="F28" s="135">
+        <v>116717.2</v>
+      </c>
+      <c r="G28" s="135">
+        <f>F28</f>
+        <v>116717.2</v>
+      </c>
+      <c r="H28" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28" s="126">
+      <c r="I28" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J28" s="127">
+      <c r="J28" s="126">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K28" s="128">
+      <c r="K28" s="127">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L28" s="129">
+      <c r="L28" s="128">
         <f t="shared" si="1"/>
         <v>116717.2</v>
       </c>
-      <c r="M28" s="130">
+      <c r="M28" s="129">
         <f t="shared" si="2"/>
         <v>120219.2</v>
       </c>
@@ -4404,154 +4498,155 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="132">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="131">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="B29" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="158" t="s">
-        <v>102</v>
-      </c>
-      <c r="D29" s="133"/>
-      <c r="E29" s="146">
+      <c r="B29" s="156" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="157" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="132"/>
+      <c r="E29" s="145">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F29" s="136">
-        <v>551941.21</v>
-      </c>
-      <c r="G29" s="136">
-        <f>300000+268500</f>
-        <v>568500</v>
-      </c>
-      <c r="H29" s="126">
+      <c r="F29" s="135">
+        <v>228744.21</v>
+      </c>
+      <c r="G29" s="133">
+        <v>235606.21</v>
+      </c>
+      <c r="H29" s="125">
         <f t="shared" si="0"/>
-        <v>-16558.790000000037</v>
-      </c>
-      <c r="I29" s="126">
+        <v>-6862</v>
+      </c>
+      <c r="I29" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="127">
+      <c r="J29" s="126">
         <f t="shared" si="4"/>
         <v>195610</v>
       </c>
-      <c r="K29" s="128">
+      <c r="K29" s="127">
         <f t="shared" si="5"/>
         <v>49693</v>
       </c>
-      <c r="L29" s="129">
+      <c r="L29" s="128">
         <f t="shared" si="1"/>
-        <v>228744.21</v>
-      </c>
-      <c r="M29" s="130">
+        <v>238441.21</v>
+      </c>
+      <c r="M29" s="129">
         <f t="shared" si="2"/>
-        <v>235606.21</v>
+        <v>245594.21</v>
       </c>
       <c r="N29" s="42">
         <f t="shared" si="7"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="188">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="131">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="B30" s="189" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="188" t="s">
-        <v>103</v>
-      </c>
-      <c r="D30" s="133" t="s">
-        <v>131</v>
-      </c>
-      <c r="E30" s="146">
+      <c r="B30" s="158" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="131" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="132" t="s">
+        <v>178</v>
+      </c>
+      <c r="E30" s="145">
         <v>3.43</v>
       </c>
-      <c r="F30" s="136">
-        <v>135066.22</v>
-      </c>
-      <c r="G30" s="136">
+      <c r="F30" s="135">
+        <v>274826.21999999997</v>
+      </c>
+      <c r="G30" s="135">
+        <f>140000*2</f>
+        <v>280000</v>
+      </c>
+      <c r="H30" s="125">
+        <f t="shared" si="0"/>
+        <v>-5173.7800000000279</v>
+      </c>
+      <c r="I30" s="125">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H30" s="126">
-        <f t="shared" si="0"/>
-        <v>135066.22</v>
-      </c>
-      <c r="I30" s="126">
-        <f t="shared" si="3"/>
-        <v>4051.9865999999997</v>
-      </c>
-      <c r="J30" s="127">
+      <c r="J30" s="126">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K30" s="128">
+      <c r="K30" s="127">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L30" s="129">
+      <c r="L30" s="128">
         <f t="shared" si="1"/>
-        <v>274826.21999999997</v>
-      </c>
-      <c r="M30" s="130">
+        <v>130534.22</v>
+      </c>
+      <c r="M30" s="129">
         <f t="shared" si="2"/>
-        <v>283071.21999999997</v>
+        <v>134450.22</v>
       </c>
       <c r="N30" s="42">
         <f t="shared" si="7"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="132">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="131">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="B31" s="159" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="160" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" s="161" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31" s="146">
+      <c r="B31" s="158" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="159" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="160" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" s="145">
         <v>2.95</v>
       </c>
-      <c r="F31" s="136">
+      <c r="F31" s="135">
         <v>116717.23</v>
       </c>
-      <c r="G31" s="136">
-        <v>116717</v>
-      </c>
-      <c r="H31" s="126">
+      <c r="G31" s="133">
+        <f>F31</f>
+        <v>116717.23</v>
+      </c>
+      <c r="H31" s="125">
         <f t="shared" si="0"/>
-        <v>0.22999999999592546</v>
-      </c>
-      <c r="I31" s="126">
+        <v>0</v>
+      </c>
+      <c r="I31" s="125">
         <f t="shared" si="3"/>
-        <v>6.8999999998777635E-3</v>
-      </c>
-      <c r="J31" s="127">
+        <v>0</v>
+      </c>
+      <c r="J31" s="126">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K31" s="128">
+      <c r="K31" s="127">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L31" s="129">
+      <c r="L31" s="128">
         <f t="shared" si="1"/>
         <v>116717.23</v>
       </c>
-      <c r="M31" s="130">
+      <c r="M31" s="129">
         <f t="shared" si="2"/>
         <v>120219.23</v>
       </c>
@@ -4560,228 +4655,228 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="123">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="122">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="B32" s="137" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="138" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="139"/>
-      <c r="E32" s="145">
+      <c r="B32" s="136" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="137" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" s="138"/>
+      <c r="E32" s="144">
         <v>5.68</v>
       </c>
-      <c r="F32" s="135">
+      <c r="F32" s="134">
         <v>224729.24</v>
       </c>
-      <c r="G32" s="136">
-        <f>F32</f>
-        <v>224729.24</v>
-      </c>
-      <c r="H32" s="126">
+      <c r="G32" s="135">
+        <v>231471.24</v>
+      </c>
+      <c r="H32" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="126">
+        <v>-6742</v>
+      </c>
+      <c r="I32" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J32" s="127">
+      <c r="J32" s="126">
         <f t="shared" si="4"/>
         <v>179204</v>
       </c>
-      <c r="K32" s="128">
+      <c r="K32" s="127">
         <f t="shared" si="5"/>
         <v>45525.2</v>
       </c>
-      <c r="L32" s="129">
+      <c r="L32" s="128">
         <f t="shared" si="1"/>
-        <v>224729.24</v>
-      </c>
-      <c r="M32" s="130">
+        <v>217987.24</v>
+      </c>
+      <c r="M32" s="129">
         <f t="shared" si="2"/>
-        <v>231471.24</v>
+        <v>224527.24</v>
       </c>
       <c r="N32" s="42">
         <f t="shared" si="7"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="207" t="s">
-        <v>106</v>
-      </c>
-      <c r="B33" s="208"/>
-      <c r="C33" s="138" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" s="138"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="135">
-        <v>116717.25</v>
-      </c>
-      <c r="G33" s="136">
-        <v>120219.25</v>
-      </c>
-      <c r="H33" s="126">
+    <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="213" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="214"/>
+      <c r="C33" s="137" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" s="137"/>
+      <c r="E33" s="123"/>
+      <c r="F33" s="134">
+        <v>113215.25</v>
+      </c>
+      <c r="G33" s="135">
+        <f>116611.25+60000</f>
+        <v>176611.25</v>
+      </c>
+      <c r="H33" s="125">
         <f t="shared" si="0"/>
-        <v>-3502</v>
-      </c>
-      <c r="I33" s="126">
+        <v>-63396</v>
+      </c>
+      <c r="I33" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J33" s="127">
+      <c r="J33" s="126">
         <f>J16</f>
         <v>93072.5</v>
       </c>
-      <c r="K33" s="128">
+      <c r="K33" s="127">
         <f>K16</f>
         <v>23644.25</v>
       </c>
-      <c r="L33" s="129">
+      <c r="L33" s="128">
         <f t="shared" si="1"/>
-        <v>113215.25</v>
-      </c>
-      <c r="M33" s="130">
+        <v>53321.25</v>
+      </c>
+      <c r="M33" s="129">
         <f t="shared" si="2"/>
-        <v>116611.25</v>
+        <v>54921.25</v>
       </c>
       <c r="N33" s="42">
         <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="O33" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="209" t="s">
-        <v>107</v>
-      </c>
-      <c r="B34" s="209"/>
-      <c r="C34" s="210"/>
-      <c r="D34" s="140"/>
-      <c r="E34" s="148">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="215" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="147">
         <f>SUM(E9:E33)</f>
         <v>99.700000000000045</v>
       </c>
-      <c r="F34" s="141">
+      <c r="F34" s="140">
         <f t="shared" ref="F34:K34" si="8">SUM(F9:F33)</f>
-        <v>5419581.4500000011</v>
-      </c>
-      <c r="G34" s="142">
+        <v>5111242.2500000009</v>
+      </c>
+      <c r="G34" s="141">
         <f t="shared" si="8"/>
-        <v>4405361.22</v>
-      </c>
-      <c r="H34" s="142">
+        <v>4494340.58</v>
+      </c>
+      <c r="H34" s="141">
         <f t="shared" si="8"/>
-        <v>1014220.23</v>
-      </c>
-      <c r="I34" s="142">
+        <v>616901.66999999993</v>
+      </c>
+      <c r="I34" s="141">
         <f t="shared" si="8"/>
-        <v>31598.546400000003</v>
-      </c>
-      <c r="J34" s="143">
+        <v>21655.513499999997</v>
+      </c>
+      <c r="J34" s="142">
         <f t="shared" si="8"/>
         <v>3238607.5</v>
       </c>
-      <c r="K34" s="142">
+      <c r="K34" s="141">
         <f t="shared" si="8"/>
         <v>822739.74999999988</v>
       </c>
-      <c r="L34" s="144">
+      <c r="L34" s="143">
         <f>SUM(L9:L26)</f>
-        <v>3717208.7100000004</v>
-      </c>
-      <c r="M34" s="144">
+        <v>3366019.7100000004</v>
+      </c>
+      <c r="M34" s="143">
         <f>SUM(M9:M33)</f>
-        <v>5260385.2500000009</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4840911.2500000009</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="49"/>
       <c r="D35" s="49"/>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="203" t="str">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="209" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="203"/>
-      <c r="E37" s="203"/>
-      <c r="F37" s="203"/>
-      <c r="G37" s="203"/>
-      <c r="H37" s="203"/>
-      <c r="I37" s="203"/>
-      <c r="J37" s="203"/>
-      <c r="K37" s="203"/>
-      <c r="L37" s="203"/>
-    </row>
-    <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="203"/>
-      <c r="D38" s="203"/>
-      <c r="E38" s="203"/>
-      <c r="F38" s="203"/>
-      <c r="G38" s="203"/>
-      <c r="H38" s="203"/>
-      <c r="I38" s="203"/>
-      <c r="J38" s="203"/>
-      <c r="K38" s="203"/>
-      <c r="L38" s="203"/>
-    </row>
-    <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="203"/>
-      <c r="D39" s="203"/>
-      <c r="E39" s="203"/>
-      <c r="F39" s="203"/>
-      <c r="G39" s="203"/>
-      <c r="H39" s="203"/>
-      <c r="I39" s="203"/>
-      <c r="J39" s="203"/>
-      <c r="K39" s="203"/>
-      <c r="L39" s="203"/>
-    </row>
-    <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="203"/>
-      <c r="D40" s="203"/>
-      <c r="E40" s="203"/>
-      <c r="F40" s="203"/>
-      <c r="G40" s="203"/>
-      <c r="H40" s="203"/>
-      <c r="I40" s="203"/>
-      <c r="J40" s="203"/>
-      <c r="K40" s="203"/>
-      <c r="L40" s="203"/>
-    </row>
-    <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="203"/>
-      <c r="D41" s="203"/>
-      <c r="E41" s="203"/>
-      <c r="F41" s="203"/>
-      <c r="G41" s="203"/>
-      <c r="H41" s="203"/>
-      <c r="I41" s="203"/>
-      <c r="J41" s="203"/>
-      <c r="K41" s="203"/>
-      <c r="L41" s="203"/>
-    </row>
-    <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="203"/>
-      <c r="D42" s="203"/>
-      <c r="E42" s="203"/>
-      <c r="F42" s="203"/>
-      <c r="G42" s="203"/>
-      <c r="H42" s="203"/>
-      <c r="I42" s="203"/>
-      <c r="J42" s="203"/>
-      <c r="K42" s="203"/>
-      <c r="L42" s="203"/>
+      <c r="D37" s="209"/>
+      <c r="E37" s="209"/>
+      <c r="F37" s="209"/>
+      <c r="G37" s="209"/>
+      <c r="H37" s="209"/>
+      <c r="I37" s="209"/>
+      <c r="J37" s="209"/>
+      <c r="K37" s="209"/>
+      <c r="L37" s="209"/>
+    </row>
+    <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="209"/>
+      <c r="D38" s="209"/>
+      <c r="E38" s="209"/>
+      <c r="F38" s="209"/>
+      <c r="G38" s="209"/>
+      <c r="H38" s="209"/>
+      <c r="I38" s="209"/>
+      <c r="J38" s="209"/>
+      <c r="K38" s="209"/>
+      <c r="L38" s="209"/>
+    </row>
+    <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="209"/>
+      <c r="D39" s="209"/>
+      <c r="E39" s="209"/>
+      <c r="F39" s="209"/>
+      <c r="G39" s="209"/>
+      <c r="H39" s="209"/>
+      <c r="I39" s="209"/>
+      <c r="J39" s="209"/>
+      <c r="K39" s="209"/>
+      <c r="L39" s="209"/>
+    </row>
+    <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="209"/>
+      <c r="D40" s="209"/>
+      <c r="E40" s="209"/>
+      <c r="F40" s="209"/>
+      <c r="G40" s="209"/>
+      <c r="H40" s="209"/>
+      <c r="I40" s="209"/>
+      <c r="J40" s="209"/>
+      <c r="K40" s="209"/>
+      <c r="L40" s="209"/>
+    </row>
+    <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="209"/>
+      <c r="D41" s="209"/>
+      <c r="E41" s="209"/>
+      <c r="F41" s="209"/>
+      <c r="G41" s="209"/>
+      <c r="H41" s="209"/>
+      <c r="I41" s="209"/>
+      <c r="J41" s="209"/>
+      <c r="K41" s="209"/>
+      <c r="L41" s="209"/>
+    </row>
+    <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="209"/>
+      <c r="D42" s="209"/>
+      <c r="E42" s="209"/>
+      <c r="F42" s="209"/>
+      <c r="G42" s="209"/>
+      <c r="H42" s="209"/>
+      <c r="I42" s="209"/>
+      <c r="J42" s="209"/>
+      <c r="K42" s="209"/>
+      <c r="L42" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -4811,183 +4906,183 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="183" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="184" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" s="179"/>
-      <c r="E4" s="179"/>
-      <c r="F4" s="179"/>
-      <c r="G4" s="180"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="185" t="s">
-        <v>162</v>
-      </c>
-      <c r="C5" s="186"/>
-      <c r="G5" s="181"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="182"/>
-      <c r="G6" s="181"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="227" t="s">
+    <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="181" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="182" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="177"/>
+      <c r="E4" s="177"/>
+      <c r="F4" s="177"/>
+      <c r="G4" s="178"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="183" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="184"/>
+      <c r="G5" s="179"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="180"/>
+      <c r="G6" s="179"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="233" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="234"/>
+      <c r="D7" s="234"/>
+      <c r="E7" s="234"/>
+      <c r="F7" s="234"/>
+      <c r="G7" s="235"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="233"/>
+      <c r="C8" s="234"/>
+      <c r="D8" s="234"/>
+      <c r="E8" s="234"/>
+      <c r="F8" s="234"/>
+      <c r="G8" s="235"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="233"/>
+      <c r="C9" s="234"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="234"/>
+      <c r="F9" s="234"/>
+      <c r="G9" s="235"/>
+    </row>
+    <row r="10" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="236"/>
+      <c r="C10" s="237"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="237"/>
+      <c r="F10" s="237"/>
+      <c r="G10" s="238"/>
+    </row>
+    <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="185" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="186" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="177"/>
+      <c r="E13" s="177"/>
+      <c r="F13" s="177"/>
+      <c r="G13" s="178"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="187" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="188" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" s="179"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="180"/>
+      <c r="G15" s="179"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="233" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="234"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="234"/>
+      <c r="F16" s="234"/>
+      <c r="G16" s="235"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="233"/>
+      <c r="C17" s="234"/>
+      <c r="D17" s="234"/>
+      <c r="E17" s="234"/>
+      <c r="F17" s="234"/>
+      <c r="G17" s="235"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="233"/>
+      <c r="C18" s="234"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="234"/>
+      <c r="G18" s="235"/>
+    </row>
+    <row r="19" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="236"/>
+      <c r="C19" s="237"/>
+      <c r="D19" s="237"/>
+      <c r="E19" s="237"/>
+      <c r="F19" s="237"/>
+      <c r="G19" s="238"/>
+    </row>
+    <row r="21" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="192" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="193" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="177"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="178"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="194" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="195"/>
+      <c r="G23" s="179"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="180"/>
+      <c r="G24" s="179"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="233" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="228"/>
-      <c r="D7" s="228"/>
-      <c r="E7" s="228"/>
-      <c r="F7" s="228"/>
-      <c r="G7" s="229"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="227"/>
-      <c r="C8" s="228"/>
-      <c r="D8" s="228"/>
-      <c r="E8" s="228"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="229"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="227"/>
-      <c r="C9" s="228"/>
-      <c r="D9" s="228"/>
-      <c r="E9" s="228"/>
-      <c r="F9" s="228"/>
-      <c r="G9" s="229"/>
-    </row>
-    <row r="10" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="230"/>
-      <c r="C10" s="231"/>
-      <c r="D10" s="231"/>
-      <c r="E10" s="231"/>
-      <c r="F10" s="231"/>
-      <c r="G10" s="232"/>
-    </row>
-    <row r="12" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="190" t="s">
-        <v>161</v>
-      </c>
-      <c r="C13" s="191" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="179"/>
-      <c r="E13" s="179"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="180"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="192" t="s">
-        <v>164</v>
-      </c>
-      <c r="C14" s="193" t="s">
-        <v>131</v>
-      </c>
-      <c r="G14" s="181"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="182"/>
-      <c r="G15" s="181"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="227" t="s">
-        <v>165</v>
-      </c>
-      <c r="C16" s="228"/>
-      <c r="D16" s="228"/>
-      <c r="E16" s="228"/>
-      <c r="F16" s="228"/>
-      <c r="G16" s="229"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="227"/>
-      <c r="C17" s="228"/>
-      <c r="D17" s="228"/>
-      <c r="E17" s="228"/>
-      <c r="F17" s="228"/>
-      <c r="G17" s="229"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="227"/>
-      <c r="C18" s="228"/>
-      <c r="D18" s="228"/>
-      <c r="E18" s="228"/>
-      <c r="F18" s="228"/>
-      <c r="G18" s="229"/>
-    </row>
-    <row r="19" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="230"/>
-      <c r="C19" s="231"/>
-      <c r="D19" s="231"/>
-      <c r="E19" s="231"/>
-      <c r="F19" s="231"/>
-      <c r="G19" s="232"/>
-    </row>
-    <row r="21" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="236" t="s">
-        <v>161</v>
-      </c>
-      <c r="C22" s="237" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="179"/>
-      <c r="E22" s="179"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="180"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="238" t="s">
-        <v>164</v>
-      </c>
-      <c r="C23" s="239"/>
-      <c r="G23" s="181"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="182"/>
-      <c r="G24" s="181"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="227" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" s="228"/>
-      <c r="D25" s="228"/>
-      <c r="E25" s="228"/>
-      <c r="F25" s="228"/>
-      <c r="G25" s="229"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="227"/>
-      <c r="C26" s="228"/>
-      <c r="D26" s="228"/>
-      <c r="E26" s="228"/>
-      <c r="F26" s="228"/>
-      <c r="G26" s="229"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="227"/>
-      <c r="C27" s="228"/>
-      <c r="D27" s="228"/>
-      <c r="E27" s="228"/>
-      <c r="F27" s="228"/>
-      <c r="G27" s="229"/>
-    </row>
-    <row r="28" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="230"/>
-      <c r="C28" s="231"/>
-      <c r="D28" s="231"/>
-      <c r="E28" s="231"/>
-      <c r="F28" s="231"/>
-      <c r="G28" s="232"/>
+      <c r="C25" s="234"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="234"/>
+      <c r="F25" s="234"/>
+      <c r="G25" s="235"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="233"/>
+      <c r="C26" s="234"/>
+      <c r="D26" s="234"/>
+      <c r="E26" s="234"/>
+      <c r="F26" s="234"/>
+      <c r="G26" s="235"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="233"/>
+      <c r="C27" s="234"/>
+      <c r="D27" s="234"/>
+      <c r="E27" s="234"/>
+      <c r="F27" s="234"/>
+      <c r="G27" s="235"/>
+    </row>
+    <row r="28" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="236"/>
+      <c r="C28" s="237"/>
+      <c r="D28" s="237"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="237"/>
+      <c r="G28" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/2026/ANATOLE FRANCE/Abril/ANATOLE-Abril.xlsx
+++ b/2026/ANATOLE FRANCE/Abril/ANATOLE-Abril.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E642800-EF5C-4B3D-A83A-CB08EBC2F1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46E732F-0F3F-4C1E-8325-77EFDA1F3F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,19 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$128</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$133</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="185">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -583,6 +578,9 @@
   </si>
   <si>
     <t>Se adeuda Marzo y Abril</t>
+  </si>
+  <si>
+    <t>Al final del mes de Enero del 2026 se contaba con una caja destinada a fondos extraordinarios de $3.232.438, en febrero se recibieron $622.371 en concepto de expensas extraordinarias, en Marzo se recibieron $674.863 y en Abril $740265,4. La suma de los tres meses arroja un total de $2.037.499,4, que sumado al saldo inicial da como resultado que de los $5.421.368,66 que se tienen en el banco $5.268.937,4 corresponden a la caja EXTRAORDINARIA</t>
   </si>
 </sst>
 </file>
@@ -886,7 +884,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1276,6 +1274,15 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1499,9 +1506,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1552,12 +1556,6 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1567,17 +1565,28 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1590,21 +1599,57 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1620,54 +1665,6 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1685,6 +1682,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1764,9 +1773,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1804,9 +1813,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1839,26 +1848,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1891,26 +1883,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2084,22 +2059,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M132"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M137"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="203" t="s">
         <v>60</v>
@@ -2108,7 +2083,7 @@
       <c r="D1" s="203"/>
       <c r="E1" s="61"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="62" t="s">
         <v>26</v>
@@ -2117,7 +2092,7 @@
       <c r="D2" s="62"/>
       <c r="E2" s="63"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
       <c r="B3" s="204" t="s">
         <v>106</v>
@@ -2126,7 +2101,7 @@
       <c r="D3" s="204"/>
       <c r="E3" s="205"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -2137,7 +2112,7 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>55</v>
       </c>
@@ -2150,7 +2125,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>56</v>
       </c>
@@ -2161,22 +2136,22 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="200" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="202" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="200"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="200"/>
-      <c r="C10" s="200"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="202"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="202"/>
+      <c r="C9" s="202"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="202"/>
+      <c r="C10" s="202"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="206" t="s">
         <v>139</v>
       </c>
@@ -2185,33 +2160,33 @@
       <c r="D13" s="206"/>
       <c r="E13" s="206"/>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="206"/>
       <c r="B14" s="206"/>
       <c r="C14" s="206"/>
       <c r="D14" s="206"/>
       <c r="E14" s="206"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="206"/>
       <c r="B15" s="206"/>
       <c r="C15" s="206"/>
       <c r="D15" s="206"/>
       <c r="E15" s="206"/>
     </row>
-    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="206"/>
       <c r="B16" s="206"/>
       <c r="C16" s="206"/>
       <c r="D16" s="206"/>
       <c r="E16" s="206"/>
     </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2220,7 +2195,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>31</v>
       </c>
@@ -2229,224 +2204,224 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="201" t="s">
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="200" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="202"/>
+      <c r="B22" s="201"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="162">
+      <c r="D22" s="161">
         <v>1038704</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="70" t="s">
         <v>115</v>
       </c>
       <c r="B23" s="114"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="162">
+      <c r="D23" s="161">
         <v>-257079.24</v>
       </c>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="70" t="s">
         <v>116</v>
       </c>
       <c r="B24" s="114"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="162">
+      <c r="D24" s="161">
         <v>0.24</v>
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="54" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="54"/>
       <c r="C25" s="54"/>
-      <c r="D25" s="163">
+      <c r="D25" s="162">
         <f>SUM(D22:D24)</f>
         <v>781625</v>
       </c>
       <c r="E25" s="102"/>
       <c r="G25" s="21"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="162"/>
+      <c r="D26" s="161"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="28"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="162"/>
+      <c r="D27" s="161"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="162"/>
+      <c r="D28" s="161"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="164"/>
+      <c r="D29" s="163"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="164"/>
+      <c r="D30" s="163"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="54" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="54"/>
       <c r="C31" s="54"/>
-      <c r="D31" s="165">
+      <c r="D31" s="164">
         <f>SUM(D26:D30)</f>
         <v>0</v>
       </c>
       <c r="E31" s="102"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="29" t="s">
         <v>1</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
-      <c r="D32" s="166"/>
+      <c r="D32" s="165"/>
       <c r="E32" s="103">
         <f>D25+D31</f>
         <v>781625</v>
       </c>
       <c r="F32" s="21"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
-      <c r="D33" s="167"/>
+      <c r="D33" s="166"/>
       <c r="E33" s="104"/>
     </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="207" t="s">
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="196" t="s">
         <v>140</v>
       </c>
-      <c r="B34" s="208"/>
+      <c r="B34" s="197"/>
       <c r="C34" s="51"/>
-      <c r="D34" s="162">
+      <c r="D34" s="161">
         <v>45000</v>
       </c>
       <c r="E34" s="105" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="207" t="s">
+    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="196" t="s">
         <v>110</v>
       </c>
-      <c r="B35" s="208"/>
+      <c r="B35" s="197"/>
       <c r="C35" s="51"/>
-      <c r="D35" s="168" t="s">
+      <c r="D35" s="167" t="s">
         <v>183</v>
       </c>
       <c r="E35" s="105"/>
     </row>
-    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
         <v>15</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
-      <c r="D36" s="169"/>
+      <c r="D36" s="168"/>
       <c r="E36" s="106">
         <f>SUM(D34:D35)</f>
         <v>45000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="34" t="s">
         <v>29</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
-      <c r="D37" s="170"/>
+      <c r="D37" s="169"/>
       <c r="E37" s="107"/>
     </row>
-    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="201" t="s">
+    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="200" t="s">
         <v>165</v>
       </c>
-      <c r="B38" s="202"/>
+      <c r="B38" s="201"/>
       <c r="C38" s="52"/>
-      <c r="D38" s="171">
+      <c r="D38" s="170">
         <v>161303</v>
       </c>
       <c r="E38" s="121" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="201" t="s">
+    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="200" t="s">
         <v>167</v>
       </c>
-      <c r="B39" s="202"/>
+      <c r="B39" s="201"/>
       <c r="C39" s="52"/>
-      <c r="D39" s="172">
+      <c r="D39" s="171">
         <v>200057</v>
       </c>
       <c r="E39" s="121" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
-      <c r="D40" s="169"/>
+      <c r="D40" s="168"/>
       <c r="E40" s="108">
         <f>SUM(D38:D39)</f>
         <v>361360</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="34" t="s">
         <v>16</v>
       </c>
       <c r="B41" s="109"/>
       <c r="C41" s="109"/>
-      <c r="D41" s="173"/>
+      <c r="D41" s="172"/>
       <c r="E41" s="110"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="51"/>
-      <c r="D42" s="199">
+      <c r="D42" s="195">
         <v>608782.14</v>
       </c>
       <c r="E42" s="115" t="s">
@@ -2454,7 +2429,7 @@
       </c>
       <c r="G42" s="89"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>155</v>
       </c>
@@ -2462,14 +2437,14 @@
         <v>111</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="174">
+      <c r="D43" s="173">
         <v>45542.1</v>
       </c>
       <c r="E43" s="115" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de ABRIL</v>
@@ -2478,7 +2453,7 @@
         <v>113</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="174">
+      <c r="D44" s="173">
         <v>86489.03</v>
       </c>
       <c r="E44" s="116" t="str">
@@ -2486,7 +2461,7 @@
         <v>Transf 13/04</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de ABRIL</v>
@@ -2495,7 +2470,7 @@
         <v>112</v>
       </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="174">
+      <c r="D45" s="173">
         <v>5060.2299999999996</v>
       </c>
       <c r="E45" s="117" t="str">
@@ -2503,231 +2478,231 @@
         <v>Transf 13/04</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
         <v>3</v>
       </c>
       <c r="B46" s="109"/>
       <c r="C46" s="109"/>
-      <c r="D46" s="175"/>
+      <c r="D46" s="174"/>
       <c r="E46" s="108">
         <f>SUM(D42:D45)</f>
         <v>745873.5</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="34" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="109"/>
       <c r="C47" s="109"/>
-      <c r="D47" s="173"/>
+      <c r="D47" s="172"/>
       <c r="E47" s="110"/>
     </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>108</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="174">
+      <c r="D48" s="173">
         <v>299191.63</v>
       </c>
       <c r="E48" s="115" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="196" t="s">
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="193" t="s">
         <v>176</v>
       </c>
-      <c r="B49" s="197"/>
+      <c r="B49" s="194"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="174">
+      <c r="D49" s="173">
         <v>49495.06</v>
       </c>
       <c r="E49" s="115" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="189" t="s">
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="B50" s="190"/>
+      <c r="B50" s="114"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="174">
+      <c r="D50" s="173">
         <v>300000</v>
       </c>
       <c r="E50" s="115" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="189" t="s">
+    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="70" t="s">
         <v>170</v>
       </c>
-      <c r="B51" s="190"/>
+      <c r="B51" s="114"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="174">
+      <c r="D51" s="173">
         <v>80000</v>
       </c>
       <c r="E51" s="115" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="189" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="B52" s="190"/>
+      <c r="B52" s="114"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="174">
+      <c r="D52" s="173">
         <v>999748.85</v>
       </c>
       <c r="E52" s="115" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="29" t="s">
         <v>4</v>
       </c>
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
-      <c r="D53" s="176"/>
+      <c r="D53" s="175"/>
       <c r="E53" s="108">
         <f>SUM(D48:D52)</f>
         <v>1728435.54</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="34" t="s">
         <v>172</v>
       </c>
       <c r="B54" s="29"/>
       <c r="C54" s="29"/>
-      <c r="D54" s="169"/>
+      <c r="D54" s="168"/>
       <c r="E54" s="111"/>
     </row>
-    <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="118" t="s">
         <v>57</v>
       </c>
       <c r="B55" s="114"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="174">
+      <c r="D55" s="173">
         <v>189500</v>
       </c>
       <c r="E55" s="146" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="118" t="s">
         <v>158</v>
       </c>
       <c r="B56" s="114"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="174">
+      <c r="D56" s="173">
         <v>31400</v>
       </c>
       <c r="E56" s="146" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="118" t="s">
         <v>157</v>
       </c>
       <c r="B57" s="114"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="174">
+      <c r="D57" s="173">
         <v>46200</v>
       </c>
       <c r="E57" s="146" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="118" t="s">
         <v>159</v>
       </c>
       <c r="B58" s="114"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="174">
+      <c r="D58" s="173">
         <v>31400</v>
       </c>
       <c r="E58" s="146" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="118" t="s">
         <v>173</v>
       </c>
-      <c r="B59" s="190"/>
+      <c r="B59" s="114"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="174">
+      <c r="D59" s="173">
         <v>99500</v>
       </c>
       <c r="E59" s="146" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="118" t="s">
         <v>174</v>
       </c>
-      <c r="B60" s="190"/>
+      <c r="B60" s="114"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="174">
+      <c r="D60" s="173">
         <v>22500</v>
       </c>
       <c r="E60" s="146" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="118" t="s">
         <v>141</v>
       </c>
       <c r="B61" s="114"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="174">
+      <c r="D61" s="173">
         <v>60000</v>
       </c>
       <c r="E61" s="146" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="191" t="s">
+    <row r="62" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="188" t="s">
         <v>166</v>
       </c>
       <c r="B62" s="114"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="174">
+      <c r="D62" s="173">
         <v>85000</v>
       </c>
       <c r="E62" s="146" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="201" t="s">
+    <row r="63" spans="1:5" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="200" t="s">
         <v>175</v>
       </c>
-      <c r="B63" s="202"/>
+      <c r="B63" s="201"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="174">
+      <c r="D63" s="173">
         <v>140000</v>
       </c>
       <c r="E63" s="146" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="29" t="s">
         <v>8</v>
       </c>
@@ -2739,38 +2714,38 @@
         <v>705500</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="34" t="s">
         <v>11</v>
       </c>
       <c r="B65" s="59"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="166"/>
+      <c r="D65" s="165"/>
       <c r="E65" s="111"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
-      <c r="D66" s="174">
+      <c r="D66" s="173">
         <v>57500</v>
       </c>
       <c r="E66" s="113"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
-      <c r="D67" s="174">
+      <c r="D67" s="173">
         <v>74836.23</v>
       </c>
       <c r="E67" s="39"/>
     </row>
-    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="50" t="s">
         <v>15</v>
       </c>
@@ -2782,14 +2757,14 @@
         <v>132336.22999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
       <c r="D69" s="67"/>
       <c r="E69" s="75"/>
     </row>
-    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="30" t="s">
         <v>46</v>
       </c>
@@ -2798,13 +2773,13 @@
       <c r="D70" s="76"/>
       <c r="E70" s="77"/>
     </row>
-    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="D71" s="78"/>
       <c r="E71" s="79"/>
       <c r="F71" s="42"/>
     </row>
-    <row r="72" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>12</v>
       </c>
@@ -2823,7 +2798,7 @@
       <c r="K72" s="89"/>
       <c r="L72" s="89"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D73" s="78"/>
       <c r="E73" s="78"/>
       <c r="H73" s="89"/>
@@ -2832,12 +2807,12 @@
       <c r="K73" s="89"/>
       <c r="L73" s="89"/>
     </row>
-    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D74" s="78"/>
       <c r="E74" s="78"/>
       <c r="H74" s="120"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
         <v>41</v>
       </c>
@@ -2846,35 +2821,35 @@
       <c r="D75" s="82"/>
       <c r="E75" s="83"/>
     </row>
-    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="201"/>
-      <c r="B76" s="202"/>
+    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="200"/>
+      <c r="B76" s="201"/>
       <c r="C76" s="5"/>
       <c r="D76" s="93"/>
       <c r="E76" s="69"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="201"/>
-      <c r="B77" s="202"/>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="200"/>
+      <c r="B77" s="201"/>
       <c r="C77" s="5"/>
       <c r="D77" s="71"/>
       <c r="E77" s="69"/>
     </row>
-    <row r="78" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="207"/>
-      <c r="B78" s="208"/>
+    <row r="78" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="196"/>
+      <c r="B78" s="197"/>
       <c r="C78" s="5"/>
       <c r="D78" s="71"/>
       <c r="E78" s="69"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="70"/>
       <c r="B79" s="72"/>
       <c r="C79" s="5"/>
       <c r="D79" s="71"/>
       <c r="E79" s="69"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="48"/>
       <c r="B80" s="47"/>
       <c r="C80" s="47"/>
@@ -2884,21 +2859,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="82" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="82" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="149" t="s">
         <v>19</v>
       </c>
       <c r="B83" s="150"/>
       <c r="C83" s="150"/>
       <c r="D83" s="151"/>
-      <c r="E83" s="152">
+      <c r="E83" s="238">
         <v>801500</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>20</v>
       </c>
@@ -2910,8 +2885,8 @@
         <v>801500</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="65" t="s">
         <v>13</v>
       </c>
@@ -2920,7 +2895,7 @@
         <v>4500130.2699999996</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="65" t="s">
         <v>14</v>
       </c>
@@ -2929,7 +2904,7 @@
         <v>4500130.2699999996</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="65" t="s">
         <v>21</v>
       </c>
@@ -2938,7 +2913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="65" t="s">
         <v>37</v>
       </c>
@@ -2947,42 +2922,42 @@
         <v>801500</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="209"/>
-      <c r="B93" s="209"/>
-      <c r="C93" s="209"/>
-      <c r="D93" s="209"/>
-      <c r="E93" s="209"/>
-    </row>
-    <row r="94" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="209"/>
-      <c r="B94" s="209"/>
-      <c r="C94" s="209"/>
-      <c r="D94" s="209"/>
-      <c r="E94" s="209"/>
-    </row>
-    <row r="95" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="209"/>
-      <c r="B95" s="209"/>
-      <c r="C95" s="209"/>
-      <c r="D95" s="209"/>
-      <c r="E95" s="209"/>
-    </row>
-    <row r="97" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="198"/>
+      <c r="B93" s="198"/>
+      <c r="C93" s="198"/>
+      <c r="D93" s="198"/>
+      <c r="E93" s="198"/>
+    </row>
+    <row r="94" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="198"/>
+      <c r="B94" s="198"/>
+      <c r="C94" s="198"/>
+      <c r="D94" s="198"/>
+      <c r="E94" s="198"/>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="198"/>
+      <c r="B95" s="198"/>
+      <c r="C95" s="198"/>
+      <c r="D95" s="198"/>
+      <c r="E95" s="198"/>
+    </row>
+    <row r="97" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="22"/>
       <c r="B97" s="90"/>
       <c r="C97" s="23"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="32"/>
       <c r="B98" s="56">
         <v>0</v>
       </c>
       <c r="C98" s="25"/>
     </row>
-    <row r="99" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="24" t="s">
         <v>7</v>
       </c>
@@ -2992,36 +2967,36 @@
       </c>
       <c r="C99" s="23"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="24"/>
       <c r="B100" s="39">
         <v>0</v>
       </c>
       <c r="C100" s="23"/>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="24" t="s">
         <v>38</v>
       </c>
       <c r="B101" s="73">
-        <f>B127</f>
+        <f>B132</f>
         <v>0</v>
       </c>
       <c r="C101" s="23"/>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="27"/>
       <c r="B102" s="46"/>
       <c r="C102" s="23"/>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="88" t="s">
         <v>42</v>
       </c>
       <c r="B103" s="46"/>
       <c r="C103" s="23"/>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="38" t="s">
         <v>22</v>
       </c>
@@ -3031,7 +3006,7 @@
       </c>
       <c r="C104" s="23"/>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="27" t="s">
         <v>23</v>
       </c>
@@ -3041,7 +3016,7 @@
       </c>
       <c r="C105" s="23"/>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="31" t="s">
         <v>8</v>
       </c>
@@ -3052,23 +3027,23 @@
       <c r="C106" s="26"/>
       <c r="D106" s="42"/>
     </row>
-    <row r="107" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="40"/>
       <c r="C107" s="26"/>
       <c r="D107" s="42"/>
       <c r="E107" s="91"/>
       <c r="F107" s="92"/>
     </row>
-    <row r="108" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="41"/>
       <c r="C108" s="26"/>
     </row>
-    <row r="109" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109"/>
       <c r="B109" s="40"/>
       <c r="C109" s="36"/>
     </row>
-    <row r="110" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="95" t="s">
         <v>132</v>
       </c>
@@ -3078,16 +3053,16 @@
       <c r="C110" s="36"/>
       <c r="D110" s="45"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="B111" s="161">
+      <c r="B111" s="160">
         <f>-B88</f>
         <v>-4500130.2699999996</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="52" t="s">
         <v>48</v>
       </c>
@@ -3096,15 +3071,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="52" t="s">
         <v>177</v>
       </c>
-      <c r="B113" s="161">
+      <c r="B113" s="160">
         <v>-76800</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="52" t="s">
         <v>117</v>
       </c>
@@ -3112,40 +3087,40 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="52" t="s">
         <v>180</v>
       </c>
-      <c r="B115" s="161">
+      <c r="B115" s="160">
         <v>-231879</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="B116" s="161">
+      <c r="B116" s="160">
         <v>-6754</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="B117" s="161">
+      <c r="B117" s="160">
         <v>-116717.02</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="52" t="s">
         <v>51</v>
       </c>
       <c r="B118" s="99">
-        <f>B127</f>
+        <f>B132</f>
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="52" t="s">
         <v>49</v>
       </c>
@@ -3154,7 +3129,7 @@
         <v>4494340.58</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="97" t="s">
         <v>44</v>
       </c>
@@ -3165,85 +3140,112 @@
       <c r="D120" s="42"/>
       <c r="E120" s="42"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="96"/>
       <c r="B121" s="96"/>
     </row>
-    <row r="122" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="210" t="s">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="96"/>
+      <c r="B122" s="96"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="235" t="s">
+        <v>184</v>
+      </c>
+      <c r="B123" s="235"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="236"/>
+      <c r="B124" s="236"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="236"/>
+      <c r="B125" s="236"/>
+    </row>
+    <row r="126" spans="1:5" ht="61.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="237"/>
+      <c r="B126" s="237"/>
+    </row>
+    <row r="127" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="199" t="s">
         <v>30</v>
       </c>
-      <c r="B123" s="210"/>
-      <c r="C123" s="210"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="210"/>
-      <c r="B124" s="210"/>
-      <c r="C124" s="210"/>
-    </row>
-    <row r="125" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="85"/>
-      <c r="B125" s="35">
+      <c r="B128" s="199"/>
+      <c r="C128" s="199"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A129" s="199"/>
+      <c r="B129" s="199"/>
+      <c r="C129" s="199"/>
+    </row>
+    <row r="130" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="85"/>
+      <c r="B130" s="35">
         <v>0</v>
       </c>
-      <c r="C125" s="35">
+      <c r="C130" s="35">
         <v>40000</v>
       </c>
-      <c r="E125" s="101"/>
-    </row>
-    <row r="126" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="85"/>
-      <c r="B126" s="87"/>
-      <c r="C126" s="84"/>
-      <c r="D126" s="101"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="43" t="s">
+      <c r="E130" s="101"/>
+    </row>
+    <row r="131" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="85"/>
+      <c r="B131" s="87"/>
+      <c r="C131" s="84"/>
+      <c r="D131" s="101"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A132" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="B127" s="86">
-        <f>SUM(B125:B126)</f>
+      <c r="B132" s="86">
+        <f>SUM(B130:B131)</f>
         <v>0</v>
       </c>
-      <c r="C127" s="44"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M128" s="7"/>
-    </row>
-    <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="209"/>
-      <c r="B129" s="209"/>
-      <c r="C129" s="209"/>
-      <c r="D129" s="209"/>
-      <c r="E129" s="209"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="209"/>
-      <c r="B130" s="209"/>
-      <c r="C130" s="209"/>
-      <c r="D130" s="209"/>
-      <c r="E130" s="209"/>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="209"/>
-      <c r="B131" s="209"/>
-      <c r="C131" s="209"/>
-      <c r="D131" s="209"/>
-      <c r="E131" s="209"/>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="209"/>
-      <c r="B132" s="209"/>
-      <c r="C132" s="209"/>
-      <c r="D132" s="209"/>
-      <c r="E132" s="209"/>
+      <c r="C132" s="44"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M133" s="7"/>
+    </row>
+    <row r="134" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="198"/>
+      <c r="B134" s="198"/>
+      <c r="C134" s="198"/>
+      <c r="D134" s="198"/>
+      <c r="E134" s="198"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135" s="198"/>
+      <c r="B135" s="198"/>
+      <c r="C135" s="198"/>
+      <c r="D135" s="198"/>
+      <c r="E135" s="198"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A136" s="198"/>
+      <c r="B136" s="198"/>
+      <c r="C136" s="198"/>
+      <c r="D136" s="198"/>
+      <c r="E136" s="198"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137" s="198"/>
+      <c r="B137" s="198"/>
+      <c r="C137" s="198"/>
+      <c r="D137" s="198"/>
+      <c r="E137" s="198"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A129:E132"/>
-    <mergeCell ref="A123:C124"/>
+    <mergeCell ref="A134:E137"/>
+    <mergeCell ref="A128:C129"/>
     <mergeCell ref="A93:E95"/>
     <mergeCell ref="A77:B77"/>
     <mergeCell ref="A76:B76"/>
@@ -3252,11 +3254,7 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A63:B63"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A123:B126"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="110" orientation="portrait" r:id="rId1"/>
@@ -3267,42 +3265,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="218"/>
-      <c r="J1" s="218"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="218"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="208"/>
+      <c r="I1" s="208"/>
+      <c r="J1" s="208"/>
+      <c r="K1" s="208"/>
+      <c r="L1" s="208"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3319,14 +3317,14 @@
       <c r="J2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="153">
+      <c r="K2" s="152">
         <v>3155000</v>
       </c>
       <c r="L2" s="94"/>
       <c r="M2" s="53"/>
       <c r="N2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3341,54 +3339,54 @@
       <c r="L3" s="57"/>
       <c r="M3" s="57"/>
     </row>
-    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="225" t="s">
+    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="216" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="226"/>
-      <c r="C4" s="226"/>
-      <c r="D4" s="226"/>
-      <c r="E4" s="226"/>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
-      <c r="H4" s="226"/>
-      <c r="I4" s="226"/>
-      <c r="J4" s="226"/>
-      <c r="K4" s="226"/>
-      <c r="L4" s="226"/>
-      <c r="M4" s="227"/>
-    </row>
-    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="228"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="200"/>
-      <c r="F5" s="200"/>
-      <c r="G5" s="200"/>
-      <c r="H5" s="200"/>
-      <c r="I5" s="200"/>
-      <c r="J5" s="200"/>
-      <c r="K5" s="200"/>
-      <c r="L5" s="200"/>
-      <c r="M5" s="229"/>
-    </row>
-    <row r="6" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="230"/>
-      <c r="B6" s="231"/>
-      <c r="C6" s="231"/>
-      <c r="D6" s="231"/>
-      <c r="E6" s="231"/>
-      <c r="F6" s="231"/>
-      <c r="G6" s="231"/>
-      <c r="H6" s="231"/>
-      <c r="I6" s="231"/>
-      <c r="J6" s="231"/>
-      <c r="K6" s="231"/>
-      <c r="L6" s="231"/>
-      <c r="M6" s="232"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B4" s="217"/>
+      <c r="C4" s="217"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="217"/>
+      <c r="F4" s="217"/>
+      <c r="G4" s="217"/>
+      <c r="H4" s="217"/>
+      <c r="I4" s="217"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="217"/>
+      <c r="L4" s="217"/>
+      <c r="M4" s="218"/>
+    </row>
+    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="219"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="202"/>
+      <c r="E5" s="202"/>
+      <c r="F5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="202"/>
+      <c r="I5" s="202"/>
+      <c r="J5" s="202"/>
+      <c r="K5" s="202"/>
+      <c r="L5" s="202"/>
+      <c r="M5" s="220"/>
+    </row>
+    <row r="6" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="221"/>
+      <c r="B6" s="222"/>
+      <c r="C6" s="222"/>
+      <c r="D6" s="222"/>
+      <c r="E6" s="222"/>
+      <c r="F6" s="222"/>
+      <c r="G6" s="222"/>
+      <c r="H6" s="222"/>
+      <c r="I6" s="222"/>
+      <c r="J6" s="222"/>
+      <c r="K6" s="222"/>
+      <c r="L6" s="222"/>
+      <c r="M6" s="223"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="211" t="s">
         <v>5</v>
       </c>
@@ -3404,50 +3402,50 @@
       <c r="E7" s="211" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="219" t="s">
+      <c r="F7" s="209" t="s">
         <v>45</v>
       </c>
       <c r="G7" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="221" t="s">
+      <c r="H7" s="212" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="219" t="s">
+      <c r="I7" s="209" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="219" t="s">
+      <c r="J7" s="209" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="223" t="s">
+      <c r="K7" s="214" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="154" t="s">
+      <c r="L7" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="217" t="s">
+      <c r="M7" s="207" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="211"/>
-      <c r="B8" s="212"/>
+      <c r="B8" s="224"/>
       <c r="C8" s="211"/>
-      <c r="D8" s="212"/>
+      <c r="D8" s="224"/>
       <c r="E8" s="211"/>
-      <c r="F8" s="220"/>
+      <c r="F8" s="210"/>
       <c r="G8" s="211"/>
-      <c r="H8" s="222"/>
-      <c r="I8" s="220"/>
-      <c r="J8" s="220"/>
-      <c r="K8" s="224"/>
+      <c r="H8" s="213"/>
+      <c r="I8" s="210"/>
+      <c r="J8" s="210"/>
+      <c r="K8" s="215"/>
       <c r="L8" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/05</v>
       </c>
-      <c r="M8" s="217"/>
-    </row>
-    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="207"/>
+    </row>
+    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="122">
         <v>1</v>
       </c>
@@ -3498,7 +3496,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="131">
         <f>A9+1</f>
         <v>2</v>
@@ -3552,7 +3550,7 @@
       </c>
       <c r="O10" s="42"/>
     </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="131">
         <f t="shared" ref="A11:A32" si="6">A10+1</f>
         <v>3</v>
@@ -3608,7 +3606,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="122">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -3659,7 +3657,7 @@
       </c>
       <c r="P12" s="42"/>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="122">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -3711,7 +3709,7 @@
       </c>
       <c r="P13" s="42"/>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="131">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -3765,7 +3763,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="122">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -3819,7 +3817,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="122">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -3872,7 +3870,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="122">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -3925,7 +3923,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="122">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -3977,7 +3975,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="122">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -4029,7 +4027,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="122">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -4082,7 +4080,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="122">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -4135,7 +4133,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="122">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -4188,7 +4186,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="131">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -4242,7 +4240,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="122">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -4290,7 +4288,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="122">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -4343,7 +4341,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="131">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -4354,7 +4352,7 @@
       <c r="C26" s="131" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="155"/>
+      <c r="D26" s="154"/>
       <c r="E26" s="145">
         <f>5.69+0.51</f>
         <v>6.2</v>
@@ -4395,7 +4393,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="131">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -4415,7 +4413,7 @@
       <c r="F27" s="133">
         <v>315013.19</v>
       </c>
-      <c r="G27" s="198"/>
+      <c r="G27" s="133"/>
       <c r="H27" s="125">
         <f t="shared" si="0"/>
         <v>315013.19</v>
@@ -4445,12 +4443,12 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="131">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="B28" s="156" t="s">
+      <c r="B28" s="155" t="s">
         <v>82</v>
       </c>
       <c r="C28" s="131" t="s">
@@ -4498,15 +4496,15 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="131">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="B29" s="156" t="s">
+      <c r="B29" s="155" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="157" t="s">
+      <c r="C29" s="156" t="s">
         <v>100</v>
       </c>
       <c r="D29" s="132"/>
@@ -4549,12 +4547,12 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="131">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="B30" s="158" t="s">
+      <c r="B30" s="157" t="s">
         <v>69</v>
       </c>
       <c r="C30" s="131" t="s">
@@ -4602,18 +4600,18 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="131">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="B31" s="158" t="s">
+      <c r="B31" s="157" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="159" t="s">
+      <c r="C31" s="158" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="160" t="s">
+      <c r="D31" s="159" t="s">
         <v>145</v>
       </c>
       <c r="E31" s="145">
@@ -4655,7 +4653,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="122">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -4705,11 +4703,11 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="213" t="s">
+    <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="225" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="214"/>
+      <c r="B33" s="226"/>
       <c r="C33" s="137" t="s">
         <v>103</v>
       </c>
@@ -4754,12 +4752,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="215" t="s">
+    <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="227" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="215"/>
-      <c r="C34" s="216"/>
+      <c r="B34" s="227"/>
+      <c r="C34" s="228"/>
       <c r="D34" s="139"/>
       <c r="E34" s="147">
         <f>SUM(E9:E33)</f>
@@ -4798,88 +4796,96 @@
         <v>4840911.2500000009</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="49"/>
       <c r="D35" s="49"/>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="209" t="str">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="198" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="209"/>
-      <c r="E37" s="209"/>
-      <c r="F37" s="209"/>
-      <c r="G37" s="209"/>
-      <c r="H37" s="209"/>
-      <c r="I37" s="209"/>
-      <c r="J37" s="209"/>
-      <c r="K37" s="209"/>
-      <c r="L37" s="209"/>
-    </row>
-    <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="209"/>
-      <c r="D38" s="209"/>
-      <c r="E38" s="209"/>
-      <c r="F38" s="209"/>
-      <c r="G38" s="209"/>
-      <c r="H38" s="209"/>
-      <c r="I38" s="209"/>
-      <c r="J38" s="209"/>
-      <c r="K38" s="209"/>
-      <c r="L38" s="209"/>
-    </row>
-    <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="209"/>
-      <c r="D39" s="209"/>
-      <c r="E39" s="209"/>
-      <c r="F39" s="209"/>
-      <c r="G39" s="209"/>
-      <c r="H39" s="209"/>
-      <c r="I39" s="209"/>
-      <c r="J39" s="209"/>
-      <c r="K39" s="209"/>
-      <c r="L39" s="209"/>
-    </row>
-    <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="209"/>
-      <c r="D40" s="209"/>
-      <c r="E40" s="209"/>
-      <c r="F40" s="209"/>
-      <c r="G40" s="209"/>
-      <c r="H40" s="209"/>
-      <c r="I40" s="209"/>
-      <c r="J40" s="209"/>
-      <c r="K40" s="209"/>
-      <c r="L40" s="209"/>
-    </row>
-    <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="209"/>
-      <c r="D41" s="209"/>
-      <c r="E41" s="209"/>
-      <c r="F41" s="209"/>
-      <c r="G41" s="209"/>
-      <c r="H41" s="209"/>
-      <c r="I41" s="209"/>
-      <c r="J41" s="209"/>
-      <c r="K41" s="209"/>
-      <c r="L41" s="209"/>
-    </row>
-    <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="209"/>
-      <c r="D42" s="209"/>
-      <c r="E42" s="209"/>
-      <c r="F42" s="209"/>
-      <c r="G42" s="209"/>
-      <c r="H42" s="209"/>
-      <c r="I42" s="209"/>
-      <c r="J42" s="209"/>
-      <c r="K42" s="209"/>
-      <c r="L42" s="209"/>
+      <c r="D37" s="198"/>
+      <c r="E37" s="198"/>
+      <c r="F37" s="198"/>
+      <c r="G37" s="198"/>
+      <c r="H37" s="198"/>
+      <c r="I37" s="198"/>
+      <c r="J37" s="198"/>
+      <c r="K37" s="198"/>
+      <c r="L37" s="198"/>
+    </row>
+    <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="198"/>
+      <c r="D38" s="198"/>
+      <c r="E38" s="198"/>
+      <c r="F38" s="198"/>
+      <c r="G38" s="198"/>
+      <c r="H38" s="198"/>
+      <c r="I38" s="198"/>
+      <c r="J38" s="198"/>
+      <c r="K38" s="198"/>
+      <c r="L38" s="198"/>
+    </row>
+    <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="198"/>
+      <c r="D39" s="198"/>
+      <c r="E39" s="198"/>
+      <c r="F39" s="198"/>
+      <c r="G39" s="198"/>
+      <c r="H39" s="198"/>
+      <c r="I39" s="198"/>
+      <c r="J39" s="198"/>
+      <c r="K39" s="198"/>
+      <c r="L39" s="198"/>
+    </row>
+    <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="198"/>
+      <c r="D40" s="198"/>
+      <c r="E40" s="198"/>
+      <c r="F40" s="198"/>
+      <c r="G40" s="198"/>
+      <c r="H40" s="198"/>
+      <c r="I40" s="198"/>
+      <c r="J40" s="198"/>
+      <c r="K40" s="198"/>
+      <c r="L40" s="198"/>
+    </row>
+    <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="198"/>
+      <c r="D41" s="198"/>
+      <c r="E41" s="198"/>
+      <c r="F41" s="198"/>
+      <c r="G41" s="198"/>
+      <c r="H41" s="198"/>
+      <c r="I41" s="198"/>
+      <c r="J41" s="198"/>
+      <c r="K41" s="198"/>
+      <c r="L41" s="198"/>
+    </row>
+    <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="198"/>
+      <c r="D42" s="198"/>
+      <c r="E42" s="198"/>
+      <c r="F42" s="198"/>
+      <c r="G42" s="198"/>
+      <c r="H42" s="198"/>
+      <c r="I42" s="198"/>
+      <c r="J42" s="198"/>
+      <c r="K42" s="198"/>
+      <c r="L42" s="198"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C37:L42"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="E1:L1"/>
     <mergeCell ref="I7:I8"/>
@@ -4889,14 +4895,6 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="A4:M6"/>
-    <mergeCell ref="C37:L42"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4906,183 +4904,183 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="181" t="s">
+    <row r="3" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="180" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="182" t="s">
+      <c r="C4" s="181" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="177"/>
-      <c r="E4" s="177"/>
-      <c r="F4" s="177"/>
-      <c r="G4" s="178"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="183" t="s">
+      <c r="D4" s="176"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="176"/>
+      <c r="G4" s="177"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="182" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="184"/>
-      <c r="G5" s="179"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="180"/>
-      <c r="G6" s="179"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="233" t="s">
+      <c r="C5" s="183"/>
+      <c r="G5" s="178"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="179"/>
+      <c r="G6" s="178"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="229" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="234"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="234"/>
-      <c r="F7" s="234"/>
-      <c r="G7" s="235"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="233"/>
-      <c r="C8" s="234"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="234"/>
-      <c r="F8" s="234"/>
-      <c r="G8" s="235"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="233"/>
-      <c r="C9" s="234"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="234"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="235"/>
-    </row>
-    <row r="10" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="236"/>
-      <c r="C10" s="237"/>
-      <c r="D10" s="237"/>
-      <c r="E10" s="237"/>
-      <c r="F10" s="237"/>
-      <c r="G10" s="238"/>
-    </row>
-    <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="185" t="s">
+      <c r="C7" s="230"/>
+      <c r="D7" s="230"/>
+      <c r="E7" s="230"/>
+      <c r="F7" s="230"/>
+      <c r="G7" s="231"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="229"/>
+      <c r="C8" s="230"/>
+      <c r="D8" s="230"/>
+      <c r="E8" s="230"/>
+      <c r="F8" s="230"/>
+      <c r="G8" s="231"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="229"/>
+      <c r="C9" s="230"/>
+      <c r="D9" s="230"/>
+      <c r="E9" s="230"/>
+      <c r="F9" s="230"/>
+      <c r="G9" s="231"/>
+    </row>
+    <row r="10" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="232"/>
+      <c r="C10" s="233"/>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="233"/>
+      <c r="G10" s="234"/>
+    </row>
+    <row r="12" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="184" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="186" t="s">
+      <c r="C13" s="185" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="177"/>
-      <c r="E13" s="177"/>
-      <c r="F13" s="177"/>
-      <c r="G13" s="178"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="187" t="s">
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="177"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="186" t="s">
         <v>151</v>
       </c>
-      <c r="C14" s="188" t="s">
+      <c r="C14" s="187" t="s">
         <v>126</v>
       </c>
-      <c r="G14" s="179"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="180"/>
-      <c r="G15" s="179"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="233" t="s">
+      <c r="G14" s="178"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="179"/>
+      <c r="G15" s="178"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="229" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="234"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="234"/>
-      <c r="F16" s="234"/>
-      <c r="G16" s="235"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="233"/>
-      <c r="C17" s="234"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="234"/>
-      <c r="F17" s="234"/>
-      <c r="G17" s="235"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="233"/>
-      <c r="C18" s="234"/>
-      <c r="D18" s="234"/>
-      <c r="E18" s="234"/>
-      <c r="F18" s="234"/>
-      <c r="G18" s="235"/>
-    </row>
-    <row r="19" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="236"/>
-      <c r="C19" s="237"/>
-      <c r="D19" s="237"/>
-      <c r="E19" s="237"/>
-      <c r="F19" s="237"/>
-      <c r="G19" s="238"/>
-    </row>
-    <row r="21" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="192" t="s">
+      <c r="C16" s="230"/>
+      <c r="D16" s="230"/>
+      <c r="E16" s="230"/>
+      <c r="F16" s="230"/>
+      <c r="G16" s="231"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="229"/>
+      <c r="C17" s="230"/>
+      <c r="D17" s="230"/>
+      <c r="E17" s="230"/>
+      <c r="F17" s="230"/>
+      <c r="G17" s="231"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="229"/>
+      <c r="C18" s="230"/>
+      <c r="D18" s="230"/>
+      <c r="E18" s="230"/>
+      <c r="F18" s="230"/>
+      <c r="G18" s="231"/>
+    </row>
+    <row r="19" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="232"/>
+      <c r="C19" s="233"/>
+      <c r="D19" s="233"/>
+      <c r="E19" s="233"/>
+      <c r="F19" s="233"/>
+      <c r="G19" s="234"/>
+    </row>
+    <row r="21" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="189" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="193" t="s">
+      <c r="C22" s="190" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="177"/>
-      <c r="E22" s="177"/>
-      <c r="F22" s="177"/>
-      <c r="G22" s="178"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="194" t="s">
+      <c r="D22" s="176"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
+      <c r="G22" s="177"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="191" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="195"/>
-      <c r="G23" s="179"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="180"/>
-      <c r="G24" s="179"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="233" t="s">
+      <c r="C23" s="192"/>
+      <c r="G23" s="178"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="179"/>
+      <c r="G24" s="178"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="229" t="s">
         <v>163</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="D25" s="234"/>
-      <c r="E25" s="234"/>
-      <c r="F25" s="234"/>
-      <c r="G25" s="235"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="233"/>
-      <c r="C26" s="234"/>
-      <c r="D26" s="234"/>
-      <c r="E26" s="234"/>
-      <c r="F26" s="234"/>
-      <c r="G26" s="235"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="233"/>
-      <c r="C27" s="234"/>
-      <c r="D27" s="234"/>
-      <c r="E27" s="234"/>
-      <c r="F27" s="234"/>
-      <c r="G27" s="235"/>
-    </row>
-    <row r="28" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="236"/>
-      <c r="C28" s="237"/>
-      <c r="D28" s="237"/>
-      <c r="E28" s="237"/>
-      <c r="F28" s="237"/>
-      <c r="G28" s="238"/>
+      <c r="C25" s="230"/>
+      <c r="D25" s="230"/>
+      <c r="E25" s="230"/>
+      <c r="F25" s="230"/>
+      <c r="G25" s="231"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="229"/>
+      <c r="C26" s="230"/>
+      <c r="D26" s="230"/>
+      <c r="E26" s="230"/>
+      <c r="F26" s="230"/>
+      <c r="G26" s="231"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="229"/>
+      <c r="C27" s="230"/>
+      <c r="D27" s="230"/>
+      <c r="E27" s="230"/>
+      <c r="F27" s="230"/>
+      <c r="G27" s="231"/>
+    </row>
+    <row r="28" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="232"/>
+      <c r="C28" s="233"/>
+      <c r="D28" s="233"/>
+      <c r="E28" s="233"/>
+      <c r="F28" s="233"/>
+      <c r="G28" s="234"/>
     </row>
   </sheetData>
   <mergeCells count="3">
